--- a/Leetcode solutions list.xlsx
+++ b/Leetcode solutions list.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Rushikesh\leetcode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C13AA54-E551-4B1C-8CA2-2BF96C24C2F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FEAE6C0-92CB-4CAA-9F57-CE5E8ED99AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E386DD19-1778-44D0-BE04-CA79BC411B80}"/>
+    <workbookView xWindow="-3840" yWindow="-1800" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{E386DD19-1778-44D0-BE04-CA79BC411B80}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Arrays &amp; hashing" sheetId="1" r:id="rId1"/>
+    <sheet name="Tow pointer" sheetId="2" r:id="rId2"/>
+    <sheet name="Sliding Window" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="74">
   <si>
     <t>Problem</t>
   </si>
@@ -79,13 +81,267 @@
   </si>
   <si>
     <t>leetcode/src/leetcode/ContainsDuplicate.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/ValidAnagram.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/TwoSum.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Group Anagrams - LeetCode</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/GroupAnagrams.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Create map of string and arraylist of string.
+For each string create a array increment the counter for each charater in the the string
+Create a String from array created above and put it in a map and the respective original string in the arraylist.</t>
+  </si>
+  <si>
+    <t>Top K Frequent Elements - LeetCode</t>
+  </si>
+  <si>
+    <t>Count max and min in the array.
+Create a array of frequency counter of lenght max-min+1, iterate over given array and increment the counter.
+(note that we will be increment the freqency of an array at postion n-min as the array length is max-min+1. smallest number will be at postion 0.)
+Keep track of max frequency while calculating
+Create an array of Arraylist, iterate over the frequency counter array and add it to the Arraylist at the position  = frequency.
+while adding element to arraylist add "min+n". where min was calculated earlier. 
+iterate over array of arrraylist, start a counter and keep adding the element from array list while the counter is greated than 0</t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/TopKFrequentElements.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Product of Array Except Self - LeetCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First we will calulate multiplecation of all the left numbers and then all the right numbers.
+Left multiplication :- Create an array and keep track of the running miltiplication. 
+Iterate over the numbers given for each element we will put the current running multiplication at the corresponding position in the array. Update the running multiplicication by multiplying with the current number. 
+Do the same from right to left differnent array.
+Multiple both the arrays. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">start index of the left multiplication will be 1
+end index of the right multuplication will be 1 </t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/ProductOfArrayExceptSelf.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Valid Sudoku - LeetCode</t>
+  </si>
+  <si>
+    <t>iterate over the sudoku using nested for loop
+create boolean 2d array of row[9][9], column[9][9], box[9][9].
+Row = i, column = j, box = (i/3)*3 + j/3. 
+update the array as following
+row[i][n], column[j][n], box[box][n]. This will confirm that the number was found in a perticular column, row and box. 
+For next number check if row[i][n], column[j][n], box[box][n] any of this value is true. is return false. else continue</t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/ValidSudoku.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Encode and Decode Strings - LeetCode</t>
+  </si>
+  <si>
+    <t>encode - append each string with length of string as prefix.
+Decode - string will start with number. That number will be the length of the string. Then you can take substring staring from number+1 with length number.</t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/EncodeAndDecodeString.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Longest Consecutive Sequence - LeetCode</t>
+  </si>
+  <si>
+    <t>Hard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">solution one :- Find max and min in the array. Create boolean an array of length Max-min+1.
+Iterate over given array and test value as true in the boolaen array for the position num-min
+therate over the boolean array can count the cosecutive true values.
+this method wokrs best when the difference between max and min count is small(1,00,000 - 10,00,000 )
+Solution two :- create a set and add all the elements to it. 
+iterate over the set. and for each element check if set cotains n-1. is yes that means the sequence start before the number and we can skip that number.
+what it exactly means that there is no need of checking the sequence from some where in the middle.
+if the set does not contain n-1. that means it could be the start of the longest sequence. when use a while loop and increment the longest sequence counter will you find n+1 value, if you dont find n+1 value in set reset the counter.  </t>
+  </si>
+  <si>
+    <t>leetcode/src/hard/LongestConsecutiveSequence.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Valid Palindrome - LeetCode</t>
+  </si>
+  <si>
+    <t>Start a left pointer and a right pointer and check if the characters are same at both the pointers. Bit the string can contain spaces or spwcial characters or symbols.
+Int hat case check if the character isLetterOrNumbe using string class default method if yes increment or decrement the pointer. and convert all the characters to small case.</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/IsPalindrome.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Two Sum II - Input Array Is Sorted - LeetCode</t>
+  </si>
+  <si>
+    <t>Ititiate 2 pointers. And start iterating over the array.
+It left+right == target = return index.
+If left+right&lt;tartget -&gt; left++
+if left+right&gt;target -&gt; right--</t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/SortedTowSum.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>3Sum - LeetCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ther key is that if you fix 1st number then remaining problem is 2 sum
+we can use 2 pointer approach here as. 
+To do that first sort the array. And iterate over it.
+For each number we can try to find -ve num using two sum </t>
+  </si>
+  <si>
+    <t xml:space="preserve">if the numbers are repeated result will contain repeated triplets. To avoid that before checking for two sum check if the number before current is same if yes continue.
+This condition may arise even after we check for 2 sum. To avoid the repetetions check if number before current left and numbe after curent right are same. if yes increment or recrement the pointer as needed. use separate while loop for each. </t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/ThreeSum.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Container With Most Water - LeetCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The limiting factor to solve this problem is the smallest height between the 2. 
+Start a left and right pointer.
+Find the area between them.
+Then we can increment or decrement the left and right pointer based on the smalled size. Which ever is the smallest we will update it. recalculate the area. </t>
+  </si>
+  <si>
+    <t>This solution can be more optimized by skipping the value that are &lt;= min.
+How? Since the limiting factor in this problem is the smallest height. If the height of next piller is smaller or equal to the current min piller the can never increase the area between them</t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/ContainerWIthMostWater.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Trapping Rain Water - LeetCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The limiting factor to solve this problem is the smallest height between the 2.
+Starter 2 pointers left and right. Move the pointer whichevers is smaller. Keep tarck of maxleft and maxright. If max&lt;current height update the max. and calulate the water like this trapperwater = trapperwater + (max-current height) </t>
+  </si>
+  <si>
+    <t>leetcode/src/hard/TrappingWater.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Best Time to Buy and Sell Stock - LeetCode</t>
+  </si>
+  <si>
+    <t>Start and initalize the pointer at index 0.
+Create a variable to keep track of the min value. curr max and Profit.
+Start incrementing right pointer by one. For each iteration check if the element at right pointer is is less than min if yes update min value tracker. If no. Update the max profit tracker with value = Max(min - arr[right], currMax)</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/BestTimeToBuyAndSellStocks.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Longest Substring Without Repeating Characters - LeetCode</t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/LongestSubtringWithoutRepeatingCharacter.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Longest Repeating Character Replacement - LeetCode</t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/LongestRepeatingCharacterReplacement.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Sliding Window Maximum - LeetCode</t>
+  </si>
+  <si>
+    <t>Permutation in String - LeetCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This problem can be solved by keeping the window "invalid". As valid window in this case measn that no chaaracters are repeadted in the window.
+Start and initalize the pointer at index 0.
+create a set which keep tack of unique characters.
+Increment the right pointer one by one. Add the the character to the set.
+While adding the character check if the character exist In the set.
+If it does calculate the the lenght of the string by comparing current max and result max. keep track if it. dont add current character or increment the right pinter.
+instead remove the left character from the set till the character at right which is repeating does not get removed.
+When the repeating character is removed from the left, keep adding the characters.
+This will make sure to keep the window valid. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This problem can be solved by keep the window valid. This can be achived by counting the most frequent characters of the string.
+If the length if substring -  max frequency &lt;= k this means that window is valid.
+How? We can replace the characters other than the most frequent character "K" time and get the longest repeating character substring.
+Initialize the left and right pointers. 
+Ititialize an array to keep track of the frequency counter for each character. 
+iterate over the string. increment the frequency in the frequency counter array. and keep track of max freq.
+if lenght of the string - max freq &lt;-k we can keep adding the element.
+else we will decrement the counter of left character and in incremement left. we will keep track of the max window size. </t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/PermutationInString.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Minimum Window Substring - LeetCode</t>
+  </si>
+  <si>
+    <t>We can find the valid window by checking the frequency of reach character in window and comparing it to the frequency of each character in window.
+create an array to track the frequency of each character. 
+whiel counting the frequency decrement the counter.
+we can create fixed lenght window equivalent to the lenght of string s2. 
+increment the frequency counter. we can decrement the the miss matched counter by 1. decrementing the miss matched counter will work like this.
+after incrementing the frequency of that character if the few freuqncy is less than or equal to 0 we will decrement the miss matched outer. then we will remove the character on left and adjust the frequency and miss matched counter accordingly. the logic to increment the miss macthed counter will work like this. after decrementing the frequency of the characer at left if the frequency of that character is less than 0 we will increment the miss matched counter. we ahve to this because extra characters are not counted as matched they are extra. and the each character frequency should be exactly same for the string to be consider as result.
+finally if the miss matched outer == 0 that is the result.</t>
+  </si>
+  <si>
+    <t>left of the permutation string in put should be greater than or equal to the length of the data string</t>
+  </si>
+  <si>
+    <t>leetcode/src/hard/MinimumWindowSubstring.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We can solve this problem by keeping the window "invalid". A valid window in this case the window which containes all the character there can be extra characters as well. 
+As soon as the window gets valid we make it in valid.
+Create map of character and frequency for string s1 and s2, initialize the maps1 with the respective frequency.
+Start left and right poiner.
+initialize need counter. need outer determines how many character we need.  
+initialize have counter. have counter determines the characters we cuurently have that are part of the permutaion string s1.
+Iterate over the string 2 and if the character at right exist in maps1.  We can add it in the maps2 and increment the frequency counter. we can increment the have counter by 1. Incrementing the have counter will work like this.
+after incrementing the frequency of that character in maps2 if the few freuqncy if less than or equal to the character frequency in map s2 we will increment the have counter. then we will remove the character on left and adjust the frequency and miss matched out accordingly. the logic to decrement the have counter will work like this. after decrementing the frequency of the characer at left if the frequency of that character is less than the character frequency in map s2 we will decreemtn the have counter. we have to this because extra characters are not counted as matched, they are extra. and the each character frequency should be exactly same for the string to be consider as result.
+if both have and need are equal and lenght is less than current lenght we can update the minimun lenght to result and update the minimum pointer.
+Instead of map we can use array to track the frequeqncy for fater execution timings, the time complexity will reduce the computational overhead for hashing in hashmap will reduce </t>
+  </si>
+  <si>
+    <t>This problem can be solved by finding the max value in the window using deque
+Deque is used because we can remove the element from last and first positions as well. For this problem we will be storing the indexed in the deque instead of actual values. because we will need to remove the element which are out of window from deque. 
+iterate over the given array and add it to the deque from last, if the given element is smaller than the current last ement in deque add it. else while given element is greater than current last ement in deque keep removing. 
+this adding and removing will create a sorted deque. where the first element will the the result for that iteration.</t>
+  </si>
+  <si>
+    <t>do not update the res for first k iterations as the result well be calculated and highest number will be found at the end of the interation k interations</t>
+  </si>
+  <si>
+    <t>leetcode/src/hard/SlidingWindowMaximum.java at main · reaper131299/leetcode</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -97,6 +353,14 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -116,7 +380,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -124,16 +388,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -471,73 +761,167 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{441B0DAF-FF1B-45C4-B4B1-CACD080E27C1}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A2:E10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.88671875" customWidth="1"/>
-    <col min="3" max="3" width="51.44140625" customWidth="1"/>
+    <col min="1" max="1" width="36.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.77734375" customWidth="1"/>
+    <col min="3" max="3" width="75.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="73.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="D2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="D3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
-        <v>6</v>
+      <c r="D4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -546,6 +930,301 @@
     <hyperlink ref="A3" r:id="rId2" display="https://leetcode.com/problems/valid-anagram/description/" xr:uid="{39E52094-9908-4A5C-8AC9-CCC1A14E5728}"/>
     <hyperlink ref="A4" r:id="rId3" display="https://leetcode.com/problems/two-sum/description/" xr:uid="{61A1352B-5B69-412A-9518-8C2026A8C1B9}"/>
     <hyperlink ref="E2" r:id="rId4" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/ContainsDuplicate.java" xr:uid="{326102EB-C732-43DA-9FB3-E0A31234E399}"/>
+    <hyperlink ref="E3" r:id="rId5" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/ValidAnagram.java" xr:uid="{66973E6F-828D-4B2F-8950-4FA0BDBEAC95}"/>
+    <hyperlink ref="E4" r:id="rId6" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/TwoSum.java" xr:uid="{277A56FB-CE8E-4DF6-B53D-A809749DFADA}"/>
+    <hyperlink ref="A5" r:id="rId7" display="https://leetcode.com/problems/group-anagrams/description/" xr:uid="{D1B7C807-6DA2-4679-ACD8-3D2F9331C36A}"/>
+    <hyperlink ref="E5" r:id="rId8" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/GroupAnagrams.java" xr:uid="{29FE2BB2-3865-422F-AD4D-0762DF9175C8}"/>
+    <hyperlink ref="A6" r:id="rId9" display="https://leetcode.com/problems/top-k-frequent-elements/description/" xr:uid="{2B65E444-857C-41E0-970A-7DA927D6312B}"/>
+    <hyperlink ref="E6" r:id="rId10" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/TopKFrequentElements.java" xr:uid="{FF881F5C-E71F-4416-A489-CD382DB037A2}"/>
+    <hyperlink ref="A7" r:id="rId11" display="https://leetcode.com/problems/product-of-array-except-self/description/" xr:uid="{40F7F3BA-5734-465E-8FE7-7EABF16C9E1D}"/>
+    <hyperlink ref="E7" r:id="rId12" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/ProductOfArrayExceptSelf.java" xr:uid="{9D4EF211-312D-4650-AA70-14E92B4CD671}"/>
+    <hyperlink ref="A8" r:id="rId13" display="https://leetcode.com/problems/valid-sudoku/description/" xr:uid="{A8AA4008-E3E3-4329-BA12-42BA57454FD9}"/>
+    <hyperlink ref="E8" r:id="rId14" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/ValidSudoku.java" xr:uid="{BD6038AA-659C-4ED3-9FCE-4D3DAF688263}"/>
+    <hyperlink ref="A9" r:id="rId15" display="https://leetcode.com/problems/encode-and-decode-strings/description/" xr:uid="{6184EBBC-9B71-444A-B820-2D822791CB67}"/>
+    <hyperlink ref="E9" r:id="rId16" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/EncodeAndDecodeString.java" xr:uid="{10E9D1AA-0444-4C2E-A6B2-C5DDC90700B8}"/>
+    <hyperlink ref="A10" r:id="rId17" display="https://leetcode.com/problems/longest-consecutive-sequence/description/" xr:uid="{3A2EE3B6-3179-4115-B25F-368FD3EEEAA8}"/>
+    <hyperlink ref="E10" r:id="rId18" display="https://github.com/reaper131299/leetcode/blob/main/src/hard/LongestConsecutiveSequence.java" xr:uid="{AD3E4AC3-65BC-46B3-89AD-3A47E29B0F9D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C831D45-5F73-4BB4-A940-A583DFCF0C9C}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.88671875" customWidth="1"/>
+    <col min="4" max="4" width="60.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="72.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="https://leetcode.com/problems/valid-palindrome/description/" xr:uid="{CF0997EC-C8C8-4252-BE61-3FA92352C342}"/>
+    <hyperlink ref="E2" r:id="rId2" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/IsPalindrome.java" xr:uid="{9A656690-0770-4E76-A955-0754F8E85F20}"/>
+    <hyperlink ref="A3" r:id="rId3" display="https://leetcode.com/problems/two-sum-ii-input-array-is-sorted/description/" xr:uid="{A534BBAB-6910-4535-8AAD-64174793615C}"/>
+    <hyperlink ref="E3" r:id="rId4" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/SortedTowSum.java" xr:uid="{75433C72-038F-4414-AC7E-503426C744BB}"/>
+    <hyperlink ref="A4" r:id="rId5" display="https://leetcode.com/problems/3sum/" xr:uid="{F0774456-8DA1-4B7B-B82F-62FAF160CC5A}"/>
+    <hyperlink ref="E4" r:id="rId6" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/ThreeSum.java" xr:uid="{BA588CEB-D395-48D3-AB5D-8A969C936013}"/>
+    <hyperlink ref="A5" r:id="rId7" display="https://leetcode.com/problems/container-with-most-water/" xr:uid="{2818DE9F-ADDD-4B93-AA1F-A8B8E6AF86EC}"/>
+    <hyperlink ref="E5" r:id="rId8" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/ContainerWIthMostWater.java" xr:uid="{49D97793-B04B-44CD-83C3-FBC3EF48F6C3}"/>
+    <hyperlink ref="A6" r:id="rId9" display="https://leetcode.com/problems/trapping-rain-water/description/" xr:uid="{C359E640-770E-46DA-853E-7F6F69BFC0CB}"/>
+    <hyperlink ref="E6" r:id="rId10" display="https://github.com/reaper131299/leetcode/blob/main/src/hard/TrappingWater.java" xr:uid="{F290A0CD-4AF2-48E0-9B23-A520523E9B85}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F2A168C-7804-47B0-992A-464C7DE20227}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="50" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="71.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.88671875" customWidth="1"/>
+    <col min="5" max="5" width="87.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="https://leetcode.com/problems/best-time-to-buy-and-sell-stock/description/" xr:uid="{5B6A5052-E466-4792-81C8-D39C534A56CF}"/>
+    <hyperlink ref="E2" r:id="rId2" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/BestTimeToBuyAndSellStocks.java" xr:uid="{5B7F9BDE-B885-4A59-8A29-EE51C9C326C5}"/>
+    <hyperlink ref="A3" r:id="rId3" display="https://leetcode.com/problems/longest-substring-without-repeating-characters/description/" xr:uid="{70478595-BD51-4557-8313-0E567AE4917A}"/>
+    <hyperlink ref="E3" r:id="rId4" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/LongestSubtringWithoutRepeatingCharacter.java" xr:uid="{C60D492D-D248-4CA4-968B-5E495FA80800}"/>
+    <hyperlink ref="A4" r:id="rId5" display="https://leetcode.com/problems/longest-repeating-character-replacement/description/" xr:uid="{E656B328-E23E-4E87-8354-0145A39F509F}"/>
+    <hyperlink ref="E4" r:id="rId6" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/LongestRepeatingCharacterReplacement.java" xr:uid="{E815522C-A80C-4406-8726-FBDA4F80439C}"/>
+    <hyperlink ref="A5" r:id="rId7" display="https://leetcode.com/problems/permutation-in-string/description/" xr:uid="{6693C9A1-565E-455A-9D84-7DDDC14D5CEA}"/>
+    <hyperlink ref="E5" r:id="rId8" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/PermutationInString.java" xr:uid="{6A803160-169B-4AFD-B7D8-8A656C473D34}"/>
+    <hyperlink ref="A6" r:id="rId9" display="https://leetcode.com/problems/minimum-window-substring/description/" xr:uid="{CABCB7D2-EDD7-44C1-986F-369D680899CE}"/>
+    <hyperlink ref="E6" r:id="rId10" display="https://github.com/reaper131299/leetcode/blob/main/src/hard/MinimumWindowSubstring.java" xr:uid="{D7BC186D-98D2-4985-A3C1-35FC4B59A8F5}"/>
+    <hyperlink ref="A7" r:id="rId11" display="https://leetcode.com/problems/sliding-window-maximum/description/" xr:uid="{41649E92-7496-40A8-91FE-BC2AD33112D4}"/>
+    <hyperlink ref="E7" r:id="rId12" display="https://github.com/reaper131299/leetcode/blob/main/src/hard/SlidingWindowMaximum.java" xr:uid="{A60EF5BD-47AB-49CB-A051-E6DA4FFDFC06}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Leetcode solutions list.xlsx
+++ b/Leetcode solutions list.xlsx
@@ -1,21 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Rushikesh\leetcode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FEAE6C0-92CB-4CAA-9F57-CE5E8ED99AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4AA1FCE-4686-4F02-8AA0-7B111C71A2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3840" yWindow="-1800" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{E386DD19-1778-44D0-BE04-CA79BC411B80}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="4" xr2:uid="{E386DD19-1778-44D0-BE04-CA79BC411B80}"/>
   </bookViews>
   <sheets>
     <sheet name="Arrays &amp; hashing" sheetId="1" r:id="rId1"/>
     <sheet name="Tow pointer" sheetId="2" r:id="rId2"/>
     <sheet name="Sliding Window" sheetId="3" r:id="rId3"/>
+    <sheet name="Stack" sheetId="6" r:id="rId4"/>
+    <sheet name="Binary Search" sheetId="7" r:id="rId5"/>
+    <sheet name="Linked List" sheetId="4" r:id="rId6"/>
+    <sheet name="Trees" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="186">
   <si>
     <t>Problem</t>
   </si>
@@ -335,6 +339,481 @@
   </si>
   <si>
     <t>leetcode/src/hard/SlidingWindowMaximum.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Reverse Linked List - LeetCode</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/ReverseLinkedList.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Merge Two Sorted Lists - LeetCode</t>
+  </si>
+  <si>
+    <t>Create a dummy node to start the linked list. Use 2 pointers to keep track of 2 linked list compare and attach the smaller node to the previous node.</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/MergeTwoSortedList.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>If one of linked list is smaller than th eother attach remaining part of the bigger list.</t>
+  </si>
+  <si>
+    <t>Reorder List - LeetCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use recursion,
+We have to plit the list in half and reverse the 2nd list then merge the 2 lists to get the result
+to keep track of slipted list initialize a valiable
+write recursive function in following way.
+If head == null that means we have reached the end of the list. which means it will be begining of the splitted list. store it in the variable we created.
+create one more global variable which keeps track of the count increment the variable one by one every recursive call. 
+create another gobal variable to know how many nodes we have to reverse that is count/2.
+recusrive funtion should return the next head.
+keep on reversing the nodes untill to be reserved count is greater than one. 
+if to be count is == 1 then nest head.next - null; this is because when to be reversedd == 1 we have partitioned the list in 2.
+now merge 2 lists. </t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/ReorderList.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Remove Nth Node From End of List - LeetCode</t>
+  </si>
+  <si>
+    <t>use recursion,
+you can reverse the linked list by using following logic 
+write recursion function such that it returns head.
+The link between then can be reversered using
+        head.next.next = head;
+        head.next = null;</t>
+  </si>
+  <si>
+    <t>We will use recursion fot his.
+Keep track of the list size using global variable.
+And anElementToBeRemoved global variable which will be equal to n
+write the recusive function such that it returns head.
+After we reach end. We start to track back and reduce toberemoved one by one.
+When element to be removed == 0 return head next instead of head.
+and when toberemoved == -1 set head.next == head next. (which is this case will be head.next.next)</t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/RemoveNthNodeFromEndOfList.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>add dummy node at the start of list such that if the element to be removed is the first node in list then 0 and -1 logic should work</t>
+  </si>
+  <si>
+    <t>Copy List with Random Pointer - LeetCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This problem can be solved using hash map
+two iterations will be needed
+1st iteration over the list create copy of each node and store it in the hash map as key == og node and value == duplicate, 
+2nd iteration iterate over the list get the key from hash map and its random node to the value of key of 1st key.random </t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/CopyListWithRandomPointer.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Add Two Numbers - LeetCode</t>
+  </si>
+  <si>
+    <t>Keep track of the carry,
+initialize 2 pointers and add the 2 pointers and carry, create node and store it in new linked list</t>
+  </si>
+  <si>
+    <t>the the 2 lists are not of same size then append remaining part of bigger list after adding carry. 
+There might be one carry remaining at the last add it to final list of its non zero</t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/AddTwoNumbers.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Linked List Cycle - LeetCode</t>
+  </si>
+  <si>
+    <t>Use floyds rabit and hare algorithm.
+Initialize the 2 pointers slow and fast. Slow will mode one step at time. Fast will move 2 steps at a time. If at any step fast == slow then cycle exists return true.</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/LinkedListCycle.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Find the Duplicate Number - LeetCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We will use floyds rabit and hare algorith.
+Star a fast and slow pointer.
+Fast will move 2 step and slow will move 1 step when fast and slow meet the cycle will be detected
+after that create another slow2 pointer and start at one.
+Move slow and fast pointer one step at time. when both meet that is the duplicate number </t>
+  </si>
+  <si>
+    <t>For this problem to solve the input is array.
+We will use elements inside the array indexes.
+E.g.:- given array is 1,3,4,2,2.
+index 0 = 1, so 1 is considered as index which in this case points to 3.
+now again 3 will be considered as index which points to 2</t>
+  </si>
+  <si>
+    <t>LRU Cache - LeetCode</t>
+  </si>
+  <si>
+    <t>We will use custom doubply linked list here.
+Common operationes needed remove first. Remove middle addlast so make a separte method for all of these.
+Put opertation. While curr cache size is less than cache size keep adding to doubly linked list and hash map.
+Get operation. search the ley in hash map if found return and remove the element add it to back.
+this will always put recently accessed element to the back of the list.and least recently element to the first.</t>
+  </si>
+  <si>
+    <t>Removing 1st and adding last to the linked list will update the head and tail of the list. Map that care fully.
+If currsize is less than max  size and if element s found just value and move it to the last. But is currsize is == max size. Update the value also, remove first and tehm add to last.</t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/LRUCache.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Merge k Sorted Lists - LeetCode</t>
+  </si>
+  <si>
+    <t>We can sequentially keep on merging 1 list with parent list  which will still be O(n) operation. But also we can merge 2 lists at a time. And reduce the number of iterations and make the process fast.
+While lists length &gt;1 
+create arraylist to add merged list. 
+keep on mering 2 lists present in th einput lists array
+convert array list a to array. so that original list is updated with the merged list and the size will reduce by half.</t>
+  </si>
+  <si>
+    <t>if the original list size is an odd number then for loop can throw arrayindex out of biund exception when getting I and i+1 list</t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/MergeKSortedLists.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Reverse Nodes in k-Group - LeetCode</t>
+  </si>
+  <si>
+    <t>This problem looks hard but easy to solve.
+To keep track of group initalize a variable. Initialize a variable head and tail. Head prev and tail next. 
+Create a dummy node and set dummy node.next  = node.
+Use while lopp (head !=null &amp;&amp; tail !=null)
+grroup ++ and keep the tail updated
+if group == k, we will ahve head prev tail next. then reverse the list between head and tail using regilar reverse alorithm. after reversal update the head prev and tail to point to the new head and tail</t>
+  </si>
+  <si>
+    <t>the list may not have size multiple k In that case we should not reverse the list.</t>
+  </si>
+  <si>
+    <t>Invert Binary Tree - LeetCode</t>
+  </si>
+  <si>
+    <t>We will use recusion,
+Recursively call reverse method, store result of left in temp
+left = right and right = left;
+return root</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/InvertBinaryTree.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Maximum Depth of Binary Tree - LeetCode</t>
+  </si>
+  <si>
+    <t>recursively add max depth method on root.left and root. Right add 1 ar each recusrion. Return 1+ math.max()</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/MaxDepthBinaryTree.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Diameter of Binary Tree - LeetCode</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/DiameterOfBinaryTree.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Balanced Binary Tree - LeetCode</t>
+  </si>
+  <si>
+    <t>Logic will be same as max depth of binary tree. With just one additional step. At every node we will calculate math.max(result, leftmax+rightMax)
+return 1+math.max(leftMax, rIghtMax)</t>
+  </si>
+  <si>
+    <t>Logic will be same as max depth of binary tree. With just one additional step. 
+We will create global variable isBalanced == true; at each node if(leftDepth, rightDepth)&gt;1 we will set isBalanced as False</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/BalancedBinaryTree.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Same Tree - LeetCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">we will use recursion.
+We will check if both nodes are equal, and store in local variable b
+if both nodes are not null we will check if left of both are equal and right of both node are equal recursively.
+We will return b &amp;&amp; result of above step
+else return b; </t>
+  </si>
+  <si>
+    <t>write condition of areNodesEqual carefully
+nodes are qual if both are null,
+if value of both of them are equal,
+Nodes are not equal if any of them is null and other is not null;</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/SameTree.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Subtree of Another Tree - LeetCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">we will use same logic as same tree problem.
+The twist will be that. We have to find substree. So we will check for same tree only if the value of both the nodes are same.
+Else we will check apply same tree logic on root.left and root.right. </t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/IsSubTree.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Lowest Common Ancestor of a Binary Search Tree - LeetCode</t>
+  </si>
+  <si>
+    <t>we can solve this but tracking the 2 given nodes p and q.We can tack them by always returning them once we find them.
+We will ahve a variable to keep track of the reult node when we find it.
+We can the method recursive on root.left and root.right. 
+Make sure you use this exact same if else sequence.
+1st if left == p and right == q or vise versa we have found the the root return root.
+2nd if root == p || root == q 
+          we will again check if any left or right are qual to any of the root. if this condition is met we have found the node return the root.
+3rd if left == p || left ==q return left;
+4th if right == p || right ==q return left;
+if none of this condition is net return null;</t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/LowestCommonAncestorOfABinarySearchTree.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Binary Tree Level Order Traversal - LeetCode</t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/BinaryTreeLevelOrderTraversal.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>2 solutions:-
+We can call the method recursively with root node and level.
+For new level we can have new array list add the node and add the list to the final list.
+Then callt he method recursive ly with root.left, level+1; root.right, level+1;
+solution 2:-
+we can use deque. so that parent nodes can be removed from start and leaf nodes can be add from last
+for initialization we can add toor to the que of root not == null;
+while(queue.size is not empty)
+size  = queue.size this will give the count of node that are present in the current level
+then for size number of iterations we will get the element and put the value to the array list and add the arraylist tot he final result. now add the root.left and root.right if they are not null</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/binary-tree-right-side-view/</t>
+  </si>
+  <si>
+    <t>Logic will be same as Binary tree level order treversal
+solution one :- update the value at level-1 index in the list with the node.vale
+solution 2:- instead of adding all the ements to the list we will just add last element to the list which is the right side</t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/BinaryTreeRightSideView.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Valid Parentheses - LeetCode</t>
+  </si>
+  <si>
+    <t>Create stack. Keep adding respective closing backets for every opening braket.
+If its closing backet pop from the stack and check for equality.</t>
+  </si>
+  <si>
+    <t>When checking for equality check if the stack is empty
+if its empty it is not a valid paranthesis
+After doen with all the characters check if stack is empty again if its not empty then its not a valid stack</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/ValidParanthesis.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Min Stack - LeetCode</t>
+  </si>
+  <si>
+    <t>we will require 2 stacks regular stack and min stack
+for push operation if the input value is less than or equal to top of the stack add it to the minstack
+For pop operation if if value that we are popping is eual to top of min stack value then remove that value from min stack</t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/MinStack.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Evaluate Reverse Polish Notation - LeetCode</t>
+  </si>
+  <si>
+    <t>iterate over given array if the element is number add it
+else if the element is and sign rake top 2 elements from the stack and do the operation store the result back into the stack</t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/EvaluateReversePolishNotation.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Generate Parentheses - LeetCode</t>
+  </si>
+  <si>
+    <t>This problem can be easily solved by recusrsion
+to keep track of open brackets and close brackets clount initialize variable
+write recursive method which does following things
+if open bracket count is less than close bracket count return
+if close brackets count == open bracket count add the string to result
+if open bracket count is &lt; then add another open bracket and increment the open bracket count
+do the same with close bracket as well</t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/GenerateParentheses.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Daily Temperatures - LeetCode</t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/DailyTemperatures.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>We will have to main tain a increment stack
+Iterate over the given array.
+If stack is empty or the current value is less than or equal to previous value add the "index" to the stack.
+Else if current value is greater than value at the top of stack then keep popping the value from the stack and update the result array</t>
+  </si>
+  <si>
+    <t>Make sure that only indexes are stored in the array. make sure after you are completed popping and updating the result add current value to stack so we don’t miss it</t>
+  </si>
+  <si>
+    <t>Car Fleet - LeetCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a 2d array where index i is a array with 2 values position and time. Time = distance/speed.
+Sort the 2d array based on the position in reverse order.
+keep track of speed of the first car of the fleet because that will be the limit factor 
+Iterate over the sorted array and if speed of the car is less than  first car of the fleet increment the fleet count. </t>
+  </si>
+  <si>
+    <t>Largest Rectangle in Histogram - LeetCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the limiting factor here is the smaller histogram
+Create a stack with 2d array
+iterate over the given array and if the height is &gt;= height at top of the stack keep adding the index and height ot the stack.
+If the height of the current bar is less than height at the top of the satck then we will start  to calculate the area;
+while height at the top of the stack is greater than the height of the current stack calculate the area like following.
+current index-stack.top index * height of the satck.top. keep track of the area. 
+while opping the stack.top is we find a height that is == current height then we willstop the iteration 
+update the stack with index before breaking the loop and current height.
+after the iteration is done. we can then iterate over the stack again in reverse order.
+then calculare the area for value present in stack as well. </t>
+  </si>
+  <si>
+    <t>leetcode/src/hard/LargestRectangleInHistogram.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Binary Search - LeetCode</t>
+  </si>
+  <si>
+    <t>Regular binary search.
+If middle == right and middle == left means value does not exist return -1;</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/BinerySearch.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Search a 2D Matrix - LeetCode</t>
+  </si>
+  <si>
+    <t>2 levels of binary search one to find the array and 2nd to find the value</t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/SearchA2DMatrix.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Koko Eating Bananas - LeetCode</t>
+  </si>
+  <si>
+    <t>We will use binary search on eating speed of koko.
+First we will iterate oven given array and find the max value.
+If size of input  == hours we will return max value.
+Else we will perform binary search on eating speed of koko. And calculate hours required to finish the bananas
+if the time is remaining then we will slow down, and if time less then we will increase the speed.
+keep track of the eating speed when ever the time is remaining as it is a potential result.</t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/KokoEatingBananas.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Find Minimum in Rotated Sorted Array - LeetCode</t>
+  </si>
+  <si>
+    <t>if the array is rotated one part will be sorted and one part will not be sorted.
+To find the minimun bumber we will have to search in unsorted part.
+if left == right then we have found the min value.
+If left &lt; right then the array is sorted return left. 
+if left &lt;= mid means array is sorted on left then we search in right partition
+if mid &lt; right measn array is sorted on right we will earch in left.</t>
+  </si>
+  <si>
+    <t>When 4th condition is met means mid &lt; right then array is sorted on right and we will search in left.
+When this condition is met. We will set right = mid not right = mid-1 because in this case the minimun value might be mid so we should not skip it.</t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/FindMinimumnRotatedSortedArray.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Search in Rotated Sorted Array - LeetCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">we will try to search the given value in the sorted part.
+if array is sorted in left part then we will check is the value is present in left side or in right. By comparing it wil boundary confition.
+else we will do the same with right part. </t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/SearchInRotatedSortedArray.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Time Based Key-Value Store - LeetCode</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>We will create a custom class with value and time stamp.
+We will create a map of key and value as arraylist of pair.
+Keep on adding the value arraylist.
+When trying to get the value. We will get the arraylist of pair for that key.
+In the array list we will perform the binary search. if the time stamp is &lt; input then it could be the potential answer and we will track it</t>
+  </si>
+  <si>
+    <t>leetcode/src/medium/TimeBasedKeyValueStore.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Median of Two Sorted Arrays - LeetCode</t>
+  </si>
+  <si>
+    <t>Looks hard but easy.
+Mediam is the middle wale of the the array. We can solve this problem by finding the correct left and right partition.
+We will take the smallest array as A and larger one as B.
+we will use binary search on array A, the elements from array A that will be the part of left partition. and remainig will be the part of array B
+how can we find that we have found correct partition.
+lets call left1 and right1 as elements of array A and left2 and right2 as elements of array B after we find the potiential partition.
+the partition to eb correct we left1&lt;right 2 and left2&lt;right1.
+once we find this condition it is easy to find the median</t>
+  </si>
+  <si>
+    <t>while finding the partition suppos the partion take all the ements from array A then
+we have to use integer.max ad right1. if no element from array A is taken as part of the partition we will take Integer.min as left1.
+similarly we will use fro array B.
+there can be odd or even number of elements in botht the arrays. 
+Calucate median based on them</t>
+  </si>
+  <si>
+    <t>leetcode/src/hard/MedianOfTwoSortedArrays.java at main · reaper131299/leetcode</t>
   </si>
 </sst>
 </file>
@@ -408,7 +887,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -421,9 +900,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -761,7 +1237,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{441B0DAF-FF1B-45C4-B4B1-CACD080E27C1}">
-  <dimension ref="A2:E10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36.21875" bestFit="1" customWidth="1"/>
@@ -771,6 +1247,23 @@
     <col min="5" max="5" width="73.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>3</v>
@@ -1036,7 +1529,7 @@
       <c r="B5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="5" t="s">
         <v>48</v>
       </c>
       <c r="D5" s="5" t="s">
@@ -1184,7 +1677,7 @@
       <c r="B6" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D6" s="2" t="s">
@@ -1201,7 +1694,7 @@
       <c r="B7" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -1230,6 +1723,794 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78D80986-F005-4960-9A02-C89870683C53}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="37.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" customWidth="1"/>
+    <col min="3" max="3" width="69.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="54.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="77.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="https://leetcode.com/problems/valid-parentheses/description/" xr:uid="{11652FC0-8413-4471-955C-9CDDE7933984}"/>
+    <hyperlink ref="E2" r:id="rId2" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/ValidParanthesis.java" xr:uid="{464B69BD-32C1-4E60-8260-FCFB9E982D91}"/>
+    <hyperlink ref="A3" r:id="rId3" display="https://leetcode.com/problems/min-stack/description/" xr:uid="{BCFE13E3-6F67-4494-8AD5-862E5C3DBAC8}"/>
+    <hyperlink ref="E3" r:id="rId4" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/MinStack.java" xr:uid="{933B98F8-3AE2-486D-AB8D-21E4543C279E}"/>
+    <hyperlink ref="A4" r:id="rId5" display="https://leetcode.com/problems/evaluate-reverse-polish-notation/description/" xr:uid="{38A64238-D219-4045-A7B3-D1731166202B}"/>
+    <hyperlink ref="E4" r:id="rId6" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/EvaluateReversePolishNotation.java" xr:uid="{2FED7BBF-2D8A-464C-82DA-9F4C124CBF37}"/>
+    <hyperlink ref="A5" r:id="rId7" display="https://leetcode.com/problems/generate-parentheses/description/" xr:uid="{8FF62987-B272-4E4A-8038-0AC79315180B}"/>
+    <hyperlink ref="E5" r:id="rId8" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/GenerateParentheses.java" xr:uid="{6AEEDF08-4F7D-4F3D-992C-BB324AA5823F}"/>
+    <hyperlink ref="A6" r:id="rId9" display="https://leetcode.com/problems/daily-temperatures/description/" xr:uid="{9C4DCF79-680B-4C43-84CA-7ADD5703435A}"/>
+    <hyperlink ref="E6" r:id="rId10" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/DailyTemperatures.java" xr:uid="{33C06429-0868-4A2F-B51F-8C7963E301DE}"/>
+    <hyperlink ref="A7" r:id="rId11" display="https://leetcode.com/problems/car-fleet/description/" xr:uid="{3BCDCB37-F30E-4A87-ABA9-88C228F88625}"/>
+    <hyperlink ref="E7" r:id="rId12" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/CarFleet.java" xr:uid="{6BE5B72B-D60A-4FE0-82D4-C34432BF9B2F}"/>
+    <hyperlink ref="A8" r:id="rId13" display="https://leetcode.com/problems/largest-rectangle-in-histogram/description/" xr:uid="{C35F2A42-BC0D-4450-8BFF-E2F7601F4A44}"/>
+    <hyperlink ref="E8" r:id="rId14" display="https://github.com/reaper131299/leetcode/blob/main/src/hard/LargestRectangleInHistogram.java" xr:uid="{087263EC-ABC7-41D2-B022-5543B0A0BF63}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87F4092A-B2FA-4797-A322-7A8E5B6A5E70}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="38.5546875" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" customWidth="1"/>
+    <col min="3" max="3" width="62.109375" customWidth="1"/>
+    <col min="4" max="4" width="69.109375" customWidth="1"/>
+    <col min="5" max="5" width="64" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="https://leetcode.com/problems/binary-search/description/" xr:uid="{41B0CE97-ADD4-4276-AA6E-0DAF6BCE75A2}"/>
+    <hyperlink ref="E2" r:id="rId2" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/BinerySearch.java" xr:uid="{EC2FAADC-C3B3-46D0-BB91-4ADA29AC8236}"/>
+    <hyperlink ref="A3" r:id="rId3" display="https://leetcode.com/problems/search-a-2d-matrix/" xr:uid="{8E3FFFE3-87EC-4121-B064-F4244833C6F6}"/>
+    <hyperlink ref="E3" r:id="rId4" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/SearchA2DMatrix.java" xr:uid="{C5907B95-4BDF-4382-83DA-402989C44C7F}"/>
+    <hyperlink ref="A4" r:id="rId5" display="https://leetcode.com/problems/koko-eating-bananas/description/" xr:uid="{9CE80503-17F0-40A5-8718-5E6B3041C69E}"/>
+    <hyperlink ref="E4" r:id="rId6" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/KokoEatingBananas.java" xr:uid="{60530478-4E80-402F-A37B-7E21F8278E58}"/>
+    <hyperlink ref="A5" r:id="rId7" display="https://leetcode.com/problems/find-minimum-in-rotated-sorted-array/description/" xr:uid="{3C8A2733-2659-4CB2-A40A-2E54A046371C}"/>
+    <hyperlink ref="E5" r:id="rId8" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/FindMinimumnRotatedSortedArray.java" xr:uid="{DDCFFB85-72F5-4C34-A40F-9F62B2B07855}"/>
+    <hyperlink ref="A6" r:id="rId9" display="https://leetcode.com/problems/search-in-rotated-sorted-array/description/" xr:uid="{92DE33AB-3BD3-46A6-8630-D2B1BD200A8D}"/>
+    <hyperlink ref="E6" r:id="rId10" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/SearchInRotatedSortedArray.java" xr:uid="{A6D1AFB9-C035-4F66-AEAC-21AEF15D8BD1}"/>
+    <hyperlink ref="A7" r:id="rId11" display="https://leetcode.com/problems/time-based-key-value-store/description/" xr:uid="{9B40D058-16C0-412F-9A54-4EE0828158A9}"/>
+    <hyperlink ref="E7" r:id="rId12" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/TimeBasedKeyValueStore.java" xr:uid="{6C5BCB59-2146-45AF-8077-35ABA502B0C3}"/>
+    <hyperlink ref="A8" r:id="rId13" display="https://leetcode.com/problems/median-of-two-sorted-arrays/description/" xr:uid="{3E04FE44-6D90-4309-AD4A-A8C94F32B735}"/>
+    <hyperlink ref="E8" r:id="rId14" display="https://github.com/reaper131299/leetcode/blob/main/src/hard/MedianOfTwoSortedArrays.java" xr:uid="{7EF1AC62-A73D-4008-9C20-726DC36838B4}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5975F89C-8640-41BF-B983-F438276F8934}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="39.33203125" customWidth="1"/>
+    <col min="3" max="3" width="87.109375" customWidth="1"/>
+    <col min="4" max="4" width="37.109375" customWidth="1"/>
+    <col min="5" max="5" width="68.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="https://leetcode.com/problems/reverse-linked-list/description/" xr:uid="{424D0148-6EB8-4421-A65E-EB7C1D0207A2}"/>
+    <hyperlink ref="E2" r:id="rId2" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/ReverseLinkedList.java" xr:uid="{9CCDBE0F-9D3A-4041-9DAF-095174E01A0E}"/>
+    <hyperlink ref="A3" r:id="rId3" display="https://leetcode.com/problems/merge-two-sorted-lists/description/" xr:uid="{FE80BD7F-8070-453A-B496-2C7DC10973F3}"/>
+    <hyperlink ref="E3" r:id="rId4" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/MergeTwoSortedList.java" xr:uid="{65C77344-41A1-424A-AEA5-2006AD87AF34}"/>
+    <hyperlink ref="A4" r:id="rId5" display="https://leetcode.com/problems/reorder-list/description/" xr:uid="{86FD1DF6-4EE3-43CD-A79B-E85597AA9D0E}"/>
+    <hyperlink ref="E4" r:id="rId6" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/ReorderList.java" xr:uid="{287288B7-3502-4BB4-85FD-9280D9D73992}"/>
+    <hyperlink ref="A5" r:id="rId7" display="https://leetcode.com/problems/remove-nth-node-from-end-of-list/description/" xr:uid="{BCAE03B2-8DB3-43FD-89CF-459668A806C5}"/>
+    <hyperlink ref="E5" r:id="rId8" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/RemoveNthNodeFromEndOfList.java" xr:uid="{39356B82-FE52-4104-A35E-AC507E6E4E0D}"/>
+    <hyperlink ref="A6" r:id="rId9" display="https://leetcode.com/problems/copy-list-with-random-pointer/" xr:uid="{14D46E76-A1E3-450A-8196-3B57AF7F5456}"/>
+    <hyperlink ref="E6" r:id="rId10" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/CopyListWithRandomPointer.java" xr:uid="{326362A5-8E58-4A95-AA08-67B5B7CECAFB}"/>
+    <hyperlink ref="A7" r:id="rId11" display="https://leetcode.com/problems/add-two-numbers/description/" xr:uid="{7A5127EC-B643-485E-B111-6A6795845BC8}"/>
+    <hyperlink ref="E7" r:id="rId12" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/AddTwoNumbers.java" xr:uid="{C0387632-CD18-4C0A-A510-5D2E0D7AA4EB}"/>
+    <hyperlink ref="A8" r:id="rId13" display="https://leetcode.com/problems/linked-list-cycle/description/" xr:uid="{2B61B7F8-E22F-43F2-9480-F2E33333F69A}"/>
+    <hyperlink ref="E8" r:id="rId14" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/LinkedListCycle.java" xr:uid="{706C45D4-EB06-44A1-B20D-4F4DB2537FB1}"/>
+    <hyperlink ref="A9" r:id="rId15" display="https://leetcode.com/problems/find-the-duplicate-number/description/" xr:uid="{E383F65C-A0CC-4CDA-85A9-A98DEFF86558}"/>
+    <hyperlink ref="E9" r:id="rId16" display="https://leetcode.com/problems/find-the-duplicate-number/description/" xr:uid="{6157C332-29D2-4AC5-83AF-F739C60FA62B}"/>
+    <hyperlink ref="A10" r:id="rId17" display="https://leetcode.com/problems/lru-cache/" xr:uid="{EBFE988D-EA92-4C13-AC17-0B62BC692738}"/>
+    <hyperlink ref="E10" r:id="rId18" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/LRUCache.java" xr:uid="{16B1F233-2051-45DE-B71B-2118FC66B5F2}"/>
+    <hyperlink ref="A11" r:id="rId19" display="https://leetcode.com/problems/merge-k-sorted-lists/" xr:uid="{1535C02B-E020-4E32-A85E-DF4D81286B7A}"/>
+    <hyperlink ref="E11" r:id="rId20" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/MergeKSortedLists.java" xr:uid="{7DC270E2-9068-42FC-A4AB-D430D077A34F}"/>
+    <hyperlink ref="A12" r:id="rId21" display="https://leetcode.com/problems/reverse-nodes-in-k-group/description/" xr:uid="{B6E2E5FB-DEAD-48AD-97FA-27F5CDAB3F8B}"/>
+    <hyperlink ref="E12" r:id="rId22" display="https://leetcode.com/problems/reverse-nodes-in-k-group/description/" xr:uid="{3E7DFFAA-7F00-4F4C-BA9D-08C09AC4439C}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{221076E7-411D-4D35-96C4-18B4D9A10664}">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" customWidth="1"/>
+    <col min="3" max="3" width="87.77734375" customWidth="1"/>
+    <col min="4" max="4" width="44.77734375" customWidth="1"/>
+    <col min="5" max="5" width="71.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="https://leetcode.com/problems/invert-binary-tree/description/" xr:uid="{9CB3F278-84A2-4893-8514-61B184910929}"/>
+    <hyperlink ref="E2" r:id="rId2" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/InvertBinaryTree.java" xr:uid="{8370B63B-F619-4C05-90F6-7C2139546258}"/>
+    <hyperlink ref="A3" r:id="rId3" display="https://leetcode.com/problems/maximum-depth-of-binary-tree/description/" xr:uid="{1906495A-BDB8-4D43-892D-1F3AFE3E40B1}"/>
+    <hyperlink ref="E3" r:id="rId4" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/MaxDepthBinaryTree.java" xr:uid="{5BC6C5CE-1FC9-412F-8384-C122EFE25925}"/>
+    <hyperlink ref="A4" r:id="rId5" display="https://leetcode.com/problems/diameter-of-binary-tree/description/" xr:uid="{B764652D-442D-407C-894D-CABA07A7F5EB}"/>
+    <hyperlink ref="E4" r:id="rId6" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/DiameterOfBinaryTree.java" xr:uid="{A24CEF47-6B84-4BAA-980C-4A390F058847}"/>
+    <hyperlink ref="A5" r:id="rId7" display="https://leetcode.com/problems/balanced-binary-tree/description/" xr:uid="{D5B8E060-86EE-499F-A138-73C309CEE304}"/>
+    <hyperlink ref="E5" r:id="rId8" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/BalancedBinaryTree.java" xr:uid="{D564C635-0C7F-4B4F-B20B-9D95F592AF84}"/>
+    <hyperlink ref="A6" r:id="rId9" display="https://leetcode.com/problems/same-tree/description/" xr:uid="{DDCE55F0-3880-472C-A4CB-BF5983E500C0}"/>
+    <hyperlink ref="E6" r:id="rId10" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/SameTree.java" xr:uid="{13BC74B8-7F2F-4A24-8FA9-596120F0E56F}"/>
+    <hyperlink ref="A7" r:id="rId11" display="https://leetcode.com/problems/subtree-of-another-tree/description/" xr:uid="{D72ECFFA-6010-4295-B62B-30CD3AB718DD}"/>
+    <hyperlink ref="E7" r:id="rId12" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/IsSubTree.java" xr:uid="{A0EE29D4-D6C2-4E60-98D0-FEE2BA6FA720}"/>
+    <hyperlink ref="A8" r:id="rId13" display="https://leetcode.com/problems/lowest-common-ancestor-of-a-binary-search-tree/description/" xr:uid="{10F4F390-02A1-43DC-8B88-10E6645F7DE7}"/>
+    <hyperlink ref="E8" r:id="rId14" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/LowestCommonAncestorOfABinarySearchTree.java" xr:uid="{3C73EE2C-7C14-47B4-AA00-09F40F3709D8}"/>
+    <hyperlink ref="A9" r:id="rId15" display="https://leetcode.com/problems/binary-tree-level-order-traversal/description/" xr:uid="{9F3DEB1D-237C-40EA-8C8A-953A8E9EECBB}"/>
+    <hyperlink ref="E9" r:id="rId16" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/BinaryTreeLevelOrderTraversal.java" xr:uid="{487753B9-120D-430E-928C-4AC6C93B9594}"/>
+    <hyperlink ref="E10" r:id="rId17" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/BinaryTreeRightSideView.java" xr:uid="{53831DB9-BF96-42A5-B864-65395160A8A9}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{ea60d57e-af5b-4752-ac57-3e4f28ca11dc}" enabled="1" method="Standard" siteId="{36da45f1-dd2c-4d1f-af13-5abe46b99921}" contentBits="0" removed="0"/>

--- a/Leetcode solutions list.xlsx
+++ b/Leetcode solutions list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Rushikesh\leetcode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4AA1FCE-4686-4F02-8AA0-7B111C71A2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47231276-BC57-46D6-8647-C518EA75743F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="4" xr2:uid="{E386DD19-1778-44D0-BE04-CA79BC411B80}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{E386DD19-1778-44D0-BE04-CA79BC411B80}"/>
   </bookViews>
   <sheets>
     <sheet name="Arrays &amp; hashing" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="Binary Search" sheetId="7" r:id="rId5"/>
     <sheet name="Linked List" sheetId="4" r:id="rId6"/>
     <sheet name="Trees" sheetId="5" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="207">
   <si>
     <t>Problem</t>
   </si>
@@ -611,9 +612,6 @@
 then for size number of iterations we will get the element and put the value to the array list and add the arraylist tot he final result. now add the root.left and root.right if they are not null</t>
   </si>
   <si>
-    <t>https://leetcode.com/problems/binary-tree-right-side-view/</t>
-  </si>
-  <si>
     <t>Logic will be same as Binary tree level order treversal
 solution one :- update the value at level-1 index in the list with the node.vale
 solution 2:- instead of adding all the ements to the list we will just add last element to the list which is the right side</t>
@@ -814,6 +812,110 @@
   </si>
   <si>
     <t>leetcode/src/hard/MedianOfTwoSortedArrays.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Binary Tree Right Side View - LeetCode</t>
+  </si>
+  <si>
+    <t>Count Good Nodes in Binary Tree - LeetCode</t>
+  </si>
+  <si>
+    <t>Use recursion
+Keep tack of prev max.
+if current value is greated than or equal to prev max increment the counter and prev max</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/medium/CountGoodNodesInBinaryTree.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Validate Binary Search Tree - LeetCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use recursion
+we will use left and right boundary to check if node is valid or not.
+Left node should be between left boundary and parent root node. Same with with right boundary </t>
+  </si>
+  <si>
+    <t>Initialize with long as the constrains say the vlaues may be 
+interger.Min_value and integer.maxvalue.</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/medium/ValidateBinarySearchTree.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Kth Smallest Element in a BST - LeetCode</t>
+  </si>
+  <si>
+    <t>We can create in order traversal to create the array and get k-1 th element.
+2nd faster solution:-
+we can have stack. We will do in order traversal iteratively so that we don’t have to go through entire binary tree.
+Keep track of current node.
+Keep on adding root to the stack until it becomes null and move the root to root.left
+if root == null that means we have reached the end of the left sub ree.
+node = pop the top element from stack. increment the counter check if the counter == k if yes return the value.
+else root == root.right</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/medium/KthSmallestElementInABST.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Construct Binary Tree from Preorder and Inorder Traversal - LeetCode</t>
+  </si>
+  <si>
+    <t>Use recursion. 
+we can iterate over the preorder array using a global counter n. And increment the counter as we recursively call the method.
+We can use left and and right pointer. 
+If left pointer is &gt;right poiner the element is null. 
+We will get the value preorder[n] and create a node.
+we will the increment the pointer.
+we will then find the index of same value in inorder array.
+then node.left = left pointer, index-1
+node.right = index+1, right pointer
+return node</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/medium/ConstructBinaryTreeFromPreorderAndInorderTraversal.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Binary Tree Maximum Path Sum - LeetCode</t>
+  </si>
+  <si>
+    <t>use recursion.
+To find amx path you have to find leftMaxPath and rightMaxPath. We will do that recursively.
+Once we get right and left max path. We will do 3 comparisons.
+Max1 = Math.max(root+leftMaxPath, root+rightMaxPath)
+Max2 = Math.max(max1, root+leftMaxPath+rightMaxPath)
+Max3 = Math.max(max2, root)
+this is because any path in the entire binary tree could be max(even the root itself max3).
+Now tack the res with max3.
+return Max between root+leftMaxPath, root+rightMaxPath and root.</t>
+  </si>
+  <si>
+    <t>even the node itself can be the max path.</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/hard/BinaryTreeMaximumPathSum.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Serialize and Deserialize Binary Tree - LeetCode</t>
+  </si>
+  <si>
+    <t>use iterations
+Serialization :- we can use linked list as queue.
+String builder to generate the string.
+Add elements to the queue. Get the size of queue. And for size iterations poll the first element of queue and add the left and right elements to queue. add the polled element to the string builder with delimeter.
+deserialize:-
+split the strign based on the delimeter.
+take the first element create node, initialize left and right pointer as 1,2.
+Add the first element to queue.
+get the element at left and right index from string[] create a node if string != null. and let to left and right respectively add the elemnts to queue, increment the left and right pointer by 2. if string == null then do not add it to queue.</t>
+  </si>
+  <si>
+    <t>while serializing check if polled element is null or not.
+While deserializing check for left and right ements and then increment the left and right counter by 2 only once</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/hard/SerializeAndDeserializeBinaryTree.java at main · reaper131299/leetcode</t>
   </si>
 </sst>
 </file>
@@ -887,7 +989,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -899,9 +1001,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1754,121 +1853,121 @@
     </row>
     <row r="2" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>158</v>
-      </c>
       <c r="D7" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B8" t="s">
         <v>34</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="D8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -1923,121 +2022,121 @@
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
         <v>165</v>
       </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="D6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B7" t="s">
         <v>178</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="D7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B8" t="s">
         <v>34</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -2307,7 +2406,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{221076E7-411D-4D35-96C4-18B4D9A10664}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -2472,19 +2571,121 @@
     </row>
     <row r="10" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>137</v>
+        <v>185</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>139</v>
+    </row>
+    <row r="11" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D15" t="s">
+        <v>201</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -2506,7 +2707,29 @@
     <hyperlink ref="A9" r:id="rId15" display="https://leetcode.com/problems/binary-tree-level-order-traversal/description/" xr:uid="{9F3DEB1D-237C-40EA-8C8A-953A8E9EECBB}"/>
     <hyperlink ref="E9" r:id="rId16" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/BinaryTreeLevelOrderTraversal.java" xr:uid="{487753B9-120D-430E-928C-4AC6C93B9594}"/>
     <hyperlink ref="E10" r:id="rId17" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/BinaryTreeRightSideView.java" xr:uid="{53831DB9-BF96-42A5-B864-65395160A8A9}"/>
+    <hyperlink ref="A10" r:id="rId18" display="https://leetcode.com/problems/binary-tree-right-side-view/" xr:uid="{115D2F38-1252-4D16-B0C2-93CCA67DE81D}"/>
+    <hyperlink ref="A11" r:id="rId19" display="https://leetcode.com/problems/count-good-nodes-in-binary-tree/description/" xr:uid="{18110539-52DF-4826-818F-28F90B19322E}"/>
+    <hyperlink ref="E11" r:id="rId20" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/medium/CountGoodNodesInBinaryTree.java" xr:uid="{2788A78D-57DB-4DB4-8174-42D16F3EA2D4}"/>
+    <hyperlink ref="A12" r:id="rId21" display="https://leetcode.com/problems/validate-binary-search-tree/description/" xr:uid="{46AE653D-3EA1-433C-B83E-B0DE59DE7B35}"/>
+    <hyperlink ref="E12" r:id="rId22" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/medium/ValidateBinarySearchTree.java" xr:uid="{ABC0CBFA-258C-46C6-A0AB-0FAE7A013F53}"/>
+    <hyperlink ref="A13" r:id="rId23" display="https://leetcode.com/problems/kth-smallest-element-in-a-bst/" xr:uid="{2F6C522C-A52F-4F50-813F-B6BF74A3E03A}"/>
+    <hyperlink ref="E13" r:id="rId24" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/medium/KthSmallestElementInABST.java" xr:uid="{9AA303EF-7784-4B51-87CF-09435E24FBE2}"/>
+    <hyperlink ref="A14" r:id="rId25" display="https://leetcode.com/problems/construct-binary-tree-from-preorder-and-inorder-traversal/description/" xr:uid="{284C98AC-B250-4C49-8872-1D53FDD13B2B}"/>
+    <hyperlink ref="E14" r:id="rId26" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/medium/ConstructBinaryTreeFromPreorderAndInorderTraversal.java" xr:uid="{764BE3F3-2C30-45A6-9ECA-6626BA876DDD}"/>
+    <hyperlink ref="A15" r:id="rId27" display="https://leetcode.com/problems/binary-tree-maximum-path-sum/" xr:uid="{25D2E43C-7E6E-494E-9DAF-B3B637F3B4E6}"/>
+    <hyperlink ref="E15" r:id="rId28" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/hard/BinaryTreeMaximumPathSum.java" xr:uid="{5A0E4BAB-0370-4507-99CA-7C324B39E92D}"/>
+    <hyperlink ref="A16" r:id="rId29" display="https://leetcode.com/problems/serialize-and-deserialize-binary-tree/" xr:uid="{CD29A3CB-8DF8-4327-81F7-464C65A86E24}"/>
+    <hyperlink ref="E16" r:id="rId30" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/hard/SerializeAndDeserializeBinaryTree.java" xr:uid="{88FDAA8C-64A9-4638-9948-9CED05F90F4C}"/>
   </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDEC9266-3BF5-42C1-9773-E32B48ADAE3F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Leetcode solutions list.xlsx
+++ b/Leetcode solutions list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Rushikesh\leetcode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47231276-BC57-46D6-8647-C518EA75743F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{589E2C6A-DADC-4B89-8C93-F33B55A28FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{E386DD19-1778-44D0-BE04-CA79BC411B80}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="9" xr2:uid="{E386DD19-1778-44D0-BE04-CA79BC411B80}"/>
   </bookViews>
   <sheets>
     <sheet name="Arrays &amp; hashing" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,9 @@
     <sheet name="Binary Search" sheetId="7" r:id="rId5"/>
     <sheet name="Linked List" sheetId="4" r:id="rId6"/>
     <sheet name="Trees" sheetId="5" r:id="rId7"/>
-    <sheet name="Sheet1" sheetId="8" r:id="rId8"/>
+    <sheet name="Tries" sheetId="8" r:id="rId8"/>
+    <sheet name="Heap, Priority Queue" sheetId="9" r:id="rId9"/>
+    <sheet name="Backtracking" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="271">
   <si>
     <t>Problem</t>
   </si>
@@ -916,6 +918,318 @@
   </si>
   <si>
     <t>leetcode/src/leetcode/hard/SerializeAndDeserializeBinaryTree.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Implement Trie (Prefix Tree) - LeetCode</t>
+  </si>
+  <si>
+    <t>"" is technically a word so the initial TrieNode mark isEndOfTheWord as true</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/medium/ImplementTrie.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Design Add and Search Words Data Structure - LeetCode</t>
+  </si>
+  <si>
+    <t>Trie data structure,
+Insert:- create a TrieNode class with fields isEndOfTheWord. And array or hashmap of length 26
+for each character of the word create a Node TrieNode and place it at the index if ch-'A' in array for add it in map.
+Search:- iterate over the characters in given word. if arrnode.arr[ch-'A'] == null that means word doen not exist return false. else we can continue update the currNode</t>
+  </si>
+  <si>
+    <t>Trie data structure,
+Insert:- create a TrieNode class with fields isEndOfTheWord. And array or hashmap of length 26
+for each character of the word create a Node TrieNode and place it at the index if ch-'A' in array for add it in map.
+Search:- since the "." can match any letter we have to search throgh every path available is we encounter "."  we can do this by recursion. if we encounter ".", iterate over all available characters and call the method again with updated pos and trieNode.</t>
+  </si>
+  <si>
+    <t>Return false of trieNode == null that means word does not exist. return isEndOfTheWord
+If pos == word.length this means we have reached the end of the word. 
+While iterating over all available paths when we encounter "." If we find matching word immidiately return true.
+But if we do not find it do not immidiately return false. iterate over the next element and after we have iterated over all the elements and still dont find any word matching. then return false.</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/medium/DesignAddAndSearchWordsDataStructure.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Word Search II - LeetCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">we will have to use combination of tire and backtracking.
+First add all the words to the trie as in other problems.
+Now use backtracking/Recursion to find the word in the board.
+Iterate over each and every character of the board. And call the back tracking method.
+to keep track of the visited cells create a boolean array of the size of the board.
+the terminating conditions are as follows, if indexes are out of bound, it cell is visited, it trienode.trienodes[board[i][j]] == null.
+March every cell as visited and unmark it before exiting the method.
+Now call the backtracking method again for the cells in 4 directions. 
+Check if the word is end of the word if yes add it to the result set. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Use map to store the trieNodes. and store the complete word when inserting to trie along with isEndOfTheWord.
+Note edge calse. But performance improvement. If we find the end if the word mark it as fasle, to avoid duplicates. 
+And if the current node does not have any child nodes then remove the node from parent. As it will never produce a complete word</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/hard/WordSearchII.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Kth Largest Element in a Stream - LeetCode</t>
+  </si>
+  <si>
+    <t>Heap and priority queue.
+Heap solution:- create variable to keep track of current capacity. Umplement a min heap. And heapify up and heapify down methods. While the current capacity is less than K keep adding elements at the alst of heap and heapify up. after that  replace the 1st element from heap with new element and heapify down.
+Priority Queue solution:- create a regular priority queue. add elements to it. if size if greated than k poll a element from que and add new. Return first element of queue</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/easy/KthLargest.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Last Stone Weight - LeetCode</t>
+  </si>
+  <si>
+    <t>we need 2 weights.
+Solution using heap max:- add all the elements to heap at last and keep heapifying up.
+When playing game while heap size is greater than 1. get the 1st element from heap and remove th elast element and add it to front. And heapify down.
+repeat it again. this will get us 2 stones. play the game add the remaining non 0 weight to the heap again at last and heapify down.
+Priority Queue:- Add all elements to priority queue, perform queue.poll twice to get the 2 elemts play the game add the remaining weight to the queue again.</t>
+  </si>
+  <si>
+    <t>No egde case but info:- regular priority queue is in increasing order. 
+To create a decreasing order priority queu you have to add reverse orfer comparator or a custom comparator when creating queue.
+You can implement the heap using arraylist. Min heap == lowest value in from == regular priority queue.
+Max heap == height value in front == reverse order priority queue. Propblems can be solved using both priority queue make the sulution cleaner</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/easy/LastStoneWeight.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>K Closest Points to Origin - LeetCode</t>
+  </si>
+  <si>
+    <t>use priority queue or heap. 
+We will using priority queue to hide the implementation and cleaner code.
+Create apoits class with x  y and dist
+Create a priority queue with comparator that compares the distance.
+Keep on adding the points to the queue.
+When we keep on polling from the queue the values will be in increasing order. 
+Poll from queue for k times.</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/medium/KClosestPointsToOrigin.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Kth Largest Element in an Array - LeetCode</t>
+  </si>
+  <si>
+    <t>Fastest solution sort the given array and return kth element.
+Using priority queue:- keep on addding elements to the priority queue if the queue size greater than k poll the first element.
+Return queue.poll</t>
+  </si>
+  <si>
+    <t>Task Scheduler - LeetCode</t>
+  </si>
+  <si>
+    <t>We need priority queue and a queue(Linekd list). First count the frequency of all the tasks. We will start with the most frequest task as it will be the most efficient way. After finding the frequency of each task. We will add the non zero freqencies to the priority queue. now iterate over the  priority queue and queue using while loop while both are not empty.
+keep track of teh timer. get first element from the priority queue if and add it the queue again add the 2nd element to the queue which will be timer+n. this tells us that when this task will be available next. now we have to bring back the tasks from the queue to priority queue if they are available. check if the current timer == queue.get(1) and add it to priority queue. why get(1)?  because we are adding 2 elements to the queue first frequency and 2nd time when it will be available next.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We will not be needing the character/task name only their frequency as we are not calulating actual sequence, only the timer </t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/medium/TaskScheduler.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/medium/KthLargestElementInAnArray.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Design Twitter - LeetCode</t>
+  </si>
+  <si>
+    <t>Create 2 classes 1.user with Queue(linekdList) and a set following, 2. tweet with time and id.
+Create a global map for keep track of users.
+I will not write rest of the methods are they are pretty straight forward.
+getNewsFeed:- create a Priorityqueue with comparater that compares time of 2 tweets.
+get the user from user map for which you want to get the feed.
+Iterate over that users follower list and add the first 10 tweets for each followee. (use iterator). 
+after adding all use add the tweets of the user himself. while adding the tweets to priority queue if the size is &gt; 10 poll a tweet.
+Create a list from the priority que using tweet id and return it.</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/medium/DesignTwitter.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Find Median from Data Stream - LeetCode</t>
+  </si>
+  <si>
+    <t>We will use the partition logic to solve this problem.
+If we find the correct partition we can find the median.
+The correct partition is when we have all the smaller values than middle in left and all the greater values than middle in right.
+To achieve this we willl need 2 priority queues/heaps. Min heap so that minimum value from right partition can be at top. and max heap so that max value from left partition can be at top. we can solve the problem like this.
+If leftMaxHeap is empty just add the value and return,
+if value being added is &lt;= the value at the top of the leftMaxHeap add the value to leftMinHeap.
+after adding we will check if the size difference between both the heaps is less than or equal to 2.(to maintain the correct partition.) if the difference is greater than 1 we will poll the value from leftMaxHeap and add it to the rightMinHeap.
+Else if the value being added is greater top of leftMaxheap then add the value to rightMinHeap. after adding we will check if the size is 0. if yes then we poll the value from rightMinHeap and add it to leftMaxHeap to maintain the partition.
+Based on the addition of size of both heaps we will determine the median. if size if odd return top value from leftMaxHeap. else return top of both the heaps/2.</t>
+  </si>
+  <si>
+    <t>We have to maintain either n and n elements in both the heaps or. n+1 and n elements in left and right heap resp. If this count changes then we have to move the elements</t>
+  </si>
+  <si>
+    <t>leetcode/src/leetcode/hard/FindMedianFromDataStream.java at main · reaper131299/leetcode</t>
+  </si>
+  <si>
+    <t>Timer starts from 0 and increases as we proceed. Which means old tweets will have least timer which will be in front in priority queue. And recent tweets will have higher timer. Which willl be at the back of prioty queue. We want the recent tweets. Which means when creating final list while iterating over priority queue add the teet ids in front of each other so they are soter in recent to old order as required.(use linked list to save some performance).
+for postTweet, and follow methods if the user does not exist create one and then do the operation.
+for getNewsFeed method id user does not exist just return empty array list.
+in user class initialize the follows set and Tweets in the constructor itself to avoid extra null checks later.</t>
+  </si>
+  <si>
+    <t>Subsets - LeetCode</t>
+  </si>
+  <si>
+    <t>Start wil empty list.
+When adding to the result set clone the list and then add it.</t>
+  </si>
+  <si>
+    <t>Combination Sum - LeetCode</t>
+  </si>
+  <si>
+    <t>Recursive method.
+For each element we have a choise if we can add a the element or we can skip it.
+Create a recusrive method which which will add the element at current position and call the recursive method agai with next position.
+remove the element and call the recursive method again with the next position.
+when the position == array.lenght ad the list to the result set</t>
+  </si>
+  <si>
+    <t>if sum == target add the array to result set. 
+Else if position == length of array or sum&gt;target return
+Note that there are 1 conditions. 
+1. Add the current element. 
+2. Add the current element again, 
+3. skip current element and add next
+Do not add next element explicitly as in the next iteration current element will be added automatically just update the position when calling the recursive method.</t>
+  </si>
+  <si>
+    <t>Permutations - LeetCode</t>
+  </si>
+  <si>
+    <t>when pos == array.length we jave a result add it to the result set.</t>
+  </si>
+  <si>
+    <t>Subsets II - LeetCode</t>
+  </si>
+  <si>
+    <t>when pos == array.length we jave a result add it to the result set.
+To get all the duplicated numbers in line so that we can skip them we. We have to sort the input.</t>
+  </si>
+  <si>
+    <t>Combination Sum II - LeetCode</t>
+  </si>
+  <si>
+    <t>when sum == target we jave a result add it to the result set.
+To get all the duplicated numbers in line so that we can skip them we. We have to sort the input.
+When using 2nd solution add i &gt; idx in for loop while skipping all the duplicate elements so that we add the first elemet element.
+Meaning we skipp all the same elements in same iteration. but do not skip same element in next iteration.
+E.g.:- 1,2,2,3
+in 1st iteration we add first 2. and skipp all the next 2's.
+but in 2nd iteration we add the 2nd 2. and not skip it.</t>
+  </si>
+  <si>
+    <t>Word Search - LeetCode</t>
+  </si>
+  <si>
+    <t>We will need a visited array to keep track of the cells we have visted before.
+Iterate over each cell of the fiven board. If character match the first character of the given string we start the recursive calling.
+mark the cell as visited.
+Call the recursive method 4 times. Once for each direction. up down left right.
+of any of the this return true we reuturn true.
+else we will unmark the visited as false and return false.</t>
+  </si>
+  <si>
+    <t>end conditions for true are if pos == length of string.
+End confitions for false are if index of is out of bounds. Char at pos != char in that cell. Or if cell is visited.</t>
+  </si>
+  <si>
+    <t>Palindrome Partitioning - LeetCode</t>
+  </si>
+  <si>
+    <t>When pos == length of string we add to resultset.</t>
+  </si>
+  <si>
+    <t>Letter Combinations of a Phone Number - LeetCode</t>
+  </si>
+  <si>
+    <t>create a Arraylist&lt;Character&gt;[] to store all the values curresponding to a number.
+Call the recursive method with epty string and pos as 0;
+for reach character in the array list for the digit as pos. append the character to the string and call the recursive method again. remove the character again from last before proceeding ahead.</t>
+  </si>
+  <si>
+    <t>Use String builder for aster tring operations.
+When pos == wtring.length add to resultset.</t>
+  </si>
+  <si>
+    <t>Apprach will be similar. 
+We will add the element at the current position calulate the sum and call the recursive method again with same position.(adding same number again)
+remove the element from last before proceeding ahead.
+We will not add the current element and skip to next position.(skipping current element).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">we have to keep track of what we have added to th. And what is not.
+Initialize a boolean array of same size as input to mark visited positions
+In recursive method. We will have for loop. For each element we will add it to the array. Mark the curresponding visited position in array increment pos and call the recursive method again.
+We will add the element only if it is not visited. Unmark element in visited after recursive call.
+Other way to solve it possible but slow.
+we will first keep calling the recursive method and increment the pos. when pso == array.length this will give us an empty array.
+for each list that the resursive method will return clone the list add the element at pos at every posible position meaning including first and last.
+add the list to result set and return it.
+</t>
+  </si>
+  <si>
+    <t>Solution will remain similar to the first question. (Subset).
+The twist hear is the number s may be duplicate and we don’t want duplicates in the solution.
+Suppose if we add element 2 to the result set and next element is again 2. If we add the first 2 and then in next iteration skip the first 2 and then again add the 2nd 2, the result will be duplicated.
+to prevent this. we can add the element as it is. call the recursive method again.remove the last element. and when it comes to skiping 1st element and adding next element we will skip all the occurences of that element using while loop.</t>
+  </si>
+  <si>
+    <t>Same solution as Subset - II.
+Sort the given input, 
+add the current element and increse the position and call the recursive emthod again,
+remove the last element.
+or skip all the occurences of that element and add next element.
+Solution 2:- bit faster.
+Base logic will remain same. But instead of calling recursive method again and again.
+we can use for loop. iterate over the current position till end. skipp all the same elements.
+add the current element and call the recursive method again with updated position and sum remove the last element.</t>
+  </si>
+  <si>
+    <t>we will start at index zero.
+Iterate over the the string using for loop starting from index current idex till end
+at each iteration we will check if the sub string is Palindrome is yes. We will add it to the array. Call the recursive method with position as cuurrent position+1. remove the string</t>
+  </si>
+  <si>
+    <t>N-Queens - LeetCode</t>
+  </si>
+  <si>
+    <t>To sovlve this prblem we will have to keep track of where the queens are placed. Columns, positive diagonal, negative diagonal
+so create 1d boolean arrays for each.
+we will call recursive method for each row recursively.
+We will start at zero. Call the recursive method.
+Iterate over the board lenght and try to palce the queen if (it doen not esist in column, positive diag, negative giag).
+if we find the position update the board with 'Q', update all the visited boolean arrays and call the recursive method with incremented value.
+remove the queen and update the visited boolean arays.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">here pos == row idx (only one queen can be placed in a row)
+if count == n add to result.
+If pos is out of index return. 
+Initialize board with '.'
+columns will be from 0 to n,
+positive giagonal value can be calculated like this row index + cloumn index
+negative diagonal can be calculated like this. Row index - columns index + n
+</t>
   </si>
 </sst>
 </file>
@@ -1541,6 +1855,176 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2DBC4A9-AA38-4BC5-98ED-CD69457A7A87}">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="33.21875" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" customWidth="1"/>
+    <col min="3" max="3" width="84.6640625" customWidth="1"/>
+    <col min="4" max="4" width="61.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="https://leetcode.com/problems/subsets/description/" xr:uid="{5C727449-D805-43E3-AFA3-96AD7C51EAB0}"/>
+    <hyperlink ref="A3" r:id="rId2" display="https://leetcode.com/problems/combination-sum/" xr:uid="{C8C097C4-8F37-445A-90BA-7DB6D210B54E}"/>
+    <hyperlink ref="A4" r:id="rId3" display="https://leetcode.com/problems/permutations/description/" xr:uid="{304E9C04-CC30-4441-864C-244F0FFB36AF}"/>
+    <hyperlink ref="A5" r:id="rId4" display="https://leetcode.com/problems/subsets-ii/description/" xr:uid="{33F36D9D-2D12-4CD3-AD9F-B7D9CE6956F7}"/>
+    <hyperlink ref="A6" r:id="rId5" display="https://leetcode.com/problems/combination-sum-ii/" xr:uid="{1A145C60-2209-450E-A3A6-8E4F77E2AB47}"/>
+    <hyperlink ref="A7" r:id="rId6" display="https://leetcode.com/problems/word-search/description/" xr:uid="{96D70F4B-9D2E-4F06-824E-CE3F36EB96E8}"/>
+    <hyperlink ref="A8" r:id="rId7" display="https://leetcode.com/problems/palindrome-partitioning/description/" xr:uid="{D9EDD481-790F-43FA-94A8-B62E829719E3}"/>
+    <hyperlink ref="A9" r:id="rId8" display="https://leetcode.com/problems/letter-combinations-of-a-phone-number/description/" xr:uid="{53B030EB-35AE-4B50-8298-181D418E748F}"/>
+    <hyperlink ref="A10" r:id="rId9" display="https://leetcode.com/problems/n-queens/" xr:uid="{BD7FC537-F4CC-4801-84BB-19B6A996B238}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C831D45-5F73-4BB4-A940-A583DFCF0C9C}">
   <dimension ref="A1:E6"/>
@@ -2727,9 +3211,261 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDEC9266-3BF5-42C1-9773-E32B48ADAE3F}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="33.33203125" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="81.5546875" customWidth="1"/>
+    <col min="4" max="4" width="74.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="https://leetcode.com/problems/implement-trie-prefix-tree/" xr:uid="{4091F9A0-8E6D-4B7A-89C3-D93397FF756D}"/>
+    <hyperlink ref="E2" r:id="rId2" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/medium/ImplementTrie.java" xr:uid="{1895FDB4-B092-46D1-9B39-42AE4AD65AEE}"/>
+    <hyperlink ref="A3" r:id="rId3" display="https://leetcode.com/problems/design-add-and-search-words-data-structure/description/" xr:uid="{2ECE93D3-8DBF-472D-9111-D4F9C88316B5}"/>
+    <hyperlink ref="E3" r:id="rId4" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/medium/DesignAddAndSearchWordsDataStructure.java" xr:uid="{E986156B-3D44-4AAC-B82B-7EF55461E40E}"/>
+    <hyperlink ref="A4" r:id="rId5" display="https://leetcode.com/problems/word-search-ii/" xr:uid="{8A2CC10B-5127-4BCE-912E-F94A9AE3AB80}"/>
+    <hyperlink ref="E4" r:id="rId6" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/hard/WordSearchII.java" xr:uid="{D926EE20-A90F-40E9-A990-6687310BF91B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CA5C3F9-742D-4041-BB06-80AADC2C17A0}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="32.21875" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="71.5546875" customWidth="1"/>
+    <col min="4" max="4" width="76.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="https://leetcode.com/problems/kth-largest-element-in-a-stream/description/" xr:uid="{81FBBF1A-0F02-49C6-83DA-B546C9D37882}"/>
+    <hyperlink ref="E2" r:id="rId2" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/easy/KthLargest.java" xr:uid="{899ACD66-2611-4099-9C4A-133C0CCCFEAB}"/>
+    <hyperlink ref="A3" r:id="rId3" display="https://leetcode.com/problems/last-stone-weight/description/" xr:uid="{47412391-6875-44FC-9041-4EC635FB9A40}"/>
+    <hyperlink ref="E3" r:id="rId4" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/easy/LastStoneWeight.java" xr:uid="{5A7B8413-121C-41FC-9329-0F285EC98EDC}"/>
+    <hyperlink ref="A4" r:id="rId5" display="https://leetcode.com/problems/k-closest-points-to-origin/description/" xr:uid="{6F75E5CC-9D37-4EA5-A1D0-F62F0551DB60}"/>
+    <hyperlink ref="E4" r:id="rId6" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/medium/KClosestPointsToOrigin.java" xr:uid="{8761A5CE-4B26-43B4-BE9F-2BE6DB9987AF}"/>
+    <hyperlink ref="A5" r:id="rId7" display="https://leetcode.com/problems/kth-largest-element-in-an-array/description/" xr:uid="{4966A595-97FA-44B6-95DA-10E903D92CE8}"/>
+    <hyperlink ref="A6" r:id="rId8" display="https://leetcode.com/problems/task-scheduler/description/" xr:uid="{2849B373-FC4E-46F4-8B13-A2635C149DF0}"/>
+    <hyperlink ref="E6" r:id="rId9" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/medium/TaskScheduler.java" xr:uid="{0ADBE634-BECC-46ED-9C01-F9DF301D77A0}"/>
+    <hyperlink ref="E5" r:id="rId10" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/medium/KthLargestElementInAnArray.java" xr:uid="{B2B5620C-6949-4700-8CA4-07340325E879}"/>
+    <hyperlink ref="A7" r:id="rId11" display="https://leetcode.com/problems/design-twitter/description/" xr:uid="{E77D91D1-39FC-4AC3-94A9-7C623986B40E}"/>
+    <hyperlink ref="E7" r:id="rId12" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/medium/DesignTwitter.java" xr:uid="{5FEF5297-7F50-4729-A396-EC1B91353A3B}"/>
+    <hyperlink ref="A8" r:id="rId13" display="https://leetcode.com/problems/find-median-from-data-stream/description/" xr:uid="{58C42322-92FE-4A4B-960A-F7CBB07BC67A}"/>
+    <hyperlink ref="E8" r:id="rId14" display="https://github.com/reaper131299/leetcode/blob/main/src/leetcode/hard/FindMedianFromDataStream.java" xr:uid="{79A308D6-27CF-4E57-8E35-6F26AE4C82B4}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Leetcode solutions list.xlsx
+++ b/Leetcode solutions list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Rushikesh\leetcode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{589E2C6A-DADC-4B89-8C93-F33B55A28FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8F5273E-E10F-4995-967E-97301FD3FD68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="9" xr2:uid="{E386DD19-1778-44D0-BE04-CA79BC411B80}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="17" xr2:uid="{E386DD19-1778-44D0-BE04-CA79BC411B80}"/>
   </bookViews>
   <sheets>
     <sheet name="Arrays &amp; hashing" sheetId="1" r:id="rId1"/>
@@ -23,8 +23,17 @@
     <sheet name="Tries" sheetId="8" r:id="rId8"/>
     <sheet name="Heap, Priority Queue" sheetId="9" r:id="rId9"/>
     <sheet name="Backtracking" sheetId="10" r:id="rId10"/>
+    <sheet name="Graph" sheetId="11" r:id="rId11"/>
+    <sheet name="Advanced Graph" sheetId="18" r:id="rId12"/>
+    <sheet name="1D Dynamic programmin" sheetId="12" r:id="rId13"/>
+    <sheet name="2D Dynamic programming" sheetId="13" r:id="rId14"/>
+    <sheet name="Greedy" sheetId="14" r:id="rId15"/>
+    <sheet name="Intervals " sheetId="15" r:id="rId16"/>
+    <sheet name="Math and Geometry" sheetId="16" r:id="rId17"/>
+    <sheet name="Bit Manipulation" sheetId="17" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -45,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="457">
   <si>
     <t>Problem</t>
   </si>
@@ -1230,6 +1239,945 @@
 positive giagonal value can be calculated like this row index + cloumn index
 negative diagonal can be calculated like this. Row index - columns index + n
 </t>
+  </si>
+  <si>
+    <t>Number of Islands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DFS on graph
+we will iterate over the given matrix. And when we encounter '1' we will do dfs on graph. and increment the count of island by 1.
+DFS function will be as follows. if current cell out of bounds or is 0 return.  We will set the value of the current cell as 0, since we have visited that cell we dint want to visit it again. Then call the recursive method again in all 4 directions. </t>
+  </si>
+  <si>
+    <t>Clone Graph - LeetCode</t>
+  </si>
+  <si>
+    <t>Iterative plus dfs.
+For every node we will create a new node set the value and add it to the map. And iterate over over original nodes neighbors call the recursive method again.
+And create a new List of neighbours and set it to nodes neighbours. Return the node.</t>
+  </si>
+  <si>
+    <t>If node already exist in the mapthen return the node
+if the number of nodes are limited use array for faster performance</t>
+  </si>
+  <si>
+    <t>Max Area of Island - LeetCode</t>
+  </si>
+  <si>
+    <t>Same solution as number as island with one small twist. We will return the area as 1 + area from reusrive method call to all 4 directition.
+do this for each cell in the matric, and update the max result with max area.</t>
+  </si>
+  <si>
+    <t>return 0 when already a water is 0, or out of bounds</t>
+  </si>
+  <si>
+    <t>Pacific Atlantic Water Flow - LeetCode</t>
+  </si>
+  <si>
+    <t>Question says water can floe is next grid height  &lt;= current grid height.
+Since we are travelling in reverse direction water will flow if current height &lt; next hegiht.
+Or water will not flow if prev height is &gt; current height
+if cell is already visited ie true then return.</t>
+  </si>
+  <si>
+    <t>instead of finding out which cell can touch pacific and atlantic water both. We will find out if oceans can reach the cell.
+We keep track of 2 separate grids for 2 different oceans.
+Top and left side are touching to pacific ocean so we will use pacific ocean grid to keep track. and
+right and bottom are touching to atlantic ocean so we will use altlantic ocean grid to keep track.
+And start from all 4 edges of the given grid. 
+And do a dfs for each cell in all 4 directions if we can reach the cell mark it visited in respective ocean grid as true.
+iterate over both pacific and atlantic grid and where both the valuesa re true add it to result set.</t>
+  </si>
+  <si>
+    <t>Surrounded Regions - LeetCode</t>
+  </si>
+  <si>
+    <t>Logic will remain similar to Pacific and atleantic water flow. 
+To keep track of safe area we will create a 2d boolean array
+We will start from all 4 edges and do a dfs. 
+For each cell mark the cell as safe in safe area array.
+And perform dfs in all 4 directions.
+when all the possible safe cells are marked. then scan over the safa area array and if cell is not safe then update the inout grid cell as X</t>
+  </si>
+  <si>
+    <t>if area is already safe || area is x || area is out of bounds return</t>
+  </si>
+  <si>
+    <t>Rotting Oranges - LeetCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is a BFS problem.
+Create a queue. We will put 2 elements in queue row and column.
+Iterate over given array and find all the oranges that are rotten and put then in queue.
+Now iterate over the queue in pair of 2. (i = 0; i&lt;size/2)
+and put the neighbouring orange to to queue (i.e. cell value is 1, and its in the bounds).
+mark that orange as ratten (i.e. 2). do this in all 4 directions.
+continue this process untill the queue is empty. </t>
+  </si>
+  <si>
+    <t>at the last we have to check if there are any fresh oranges if yes return false.
+Initially is the queue is empty we have to check if there are any freshaoranges remaining. That means oranges can never get rotten Is yes return false.
+instead of abouve To save some time we can keep track track of fresh oranges.
+if at the last fresh oranges  == 0 then return true else false.
+By his logic timer will be ahead by 1 since even if all the oranges are rooten logic will check of neighbours of last orange, so return the result as res-1.</t>
+  </si>
+  <si>
+    <t>Walls and Gates - LeetCode</t>
+  </si>
+  <si>
+    <t>This question is same as water and  treasure
+Same logic as rotten oranges.
+Put all the Treasure cells in queue.Start the distance as one.
+start iterating over queue. For each neighbouring cells add the cell to queue if the  cell is in bounds and cell value is land. before adding the cell to queue update its value with distance.
+after current iteration over the queue is completed update the distance+1.</t>
+  </si>
+  <si>
+    <t>for problem rottign oranges and walls and gates adding cell to queue means
+queue.add(row), queue.add(column)</t>
+  </si>
+  <si>
+    <t>Course Schedule - LeetCode</t>
+  </si>
+  <si>
+    <t>When iterating over set use iterator so that you don’t get concurrent manipulation exception. 
+The return conditions are as folllows in the this order.
+1. if neighbours for that couse is empty that means that course can be completed. So return true.
+2. If visited then return false. that means that course has a cercular dependency.
+We remove the completed course from the set to reduce the time required for the program. and we can do that becuase. if the course can be completed then the dependent course also can be completed without any problem. so we can safely remove the neightbours</t>
+  </si>
+  <si>
+    <t>Course Schedule II - LeetCode</t>
+  </si>
+  <si>
+    <t>same as course schedule</t>
+  </si>
+  <si>
+    <t>Topological sort:- 
+We will need adjecency list, adjecensy list is a data structre for graphs. Where we can keep track of nodes and their neighbours.
+Create a adjecency list while iterating over the given array using set. You can use map&lt;integer, set&gt; or set[] to create it.
+Iterate over the adjecency list.
+and for each course. call the recusrive method which check if course can be completed.
+create an boolean array to keep track of visited courses
+the method will be as follows. 
+Mark the course as visited. for each neighbours of that course call the recusrive mehod again. if that returns fasle then 
+we can terminate the program and return fasle. return false.
+if it is true. remove that course from the neighboures set. and continue to next course. if iterated over all the neightbours then unmark in visted return true.</t>
+  </si>
+  <si>
+    <t>Topological sort:- 
+Same solution as course schedule.
+One small addition we create added to result boolean array to track if teh course is already added to result or not
+before returning true(if course neighbours is empty or iterated over all course negihbours successfully), we add the course to the result list if it is already not added.</t>
+  </si>
+  <si>
+    <t>Redundant Connection - LeetCode</t>
+  </si>
+  <si>
+    <t>Union find.
+To check if the connection is redundant in tree. We have to find a cycle in tree.
+To find a cycle we can cehck if the 2 nodes are already part of the same component.
+Create 2 arrays parent and rank.
+initially reach node will be parent of it self as there are no edges.
+rank will be 1.
+For for each edge in given array.
+we will find the parent of each of the node in edge. aParent, bParent
+if parents are same that means both nodes are part of same component so return the edge.(this is find operation)
+(union operation.)
+now we will check which node has higher rank, we will merge the other node in to that.
+we will add both the ranks and set it to respective position. and we will update the parent[aParent] = bParent.(dependign onwhich rank is higher)
+Find parent function();
+we have to to get top most parent the in heirarchy.p = parent[c], to do that we have to iterate while p != parent[p]. 
+p = parent[p]. because p == parent[p] whill get satislifed only when the element is the parent most element.(parent of self)</t>
+  </si>
+  <si>
+    <t>write find function correctly to get the parent most element. Not just immidiet parent
+And when setting the parent value in parent array make sure that you set it at the position of the parent(aParent/bParent) not child(a/b).</t>
+  </si>
+  <si>
+    <t>Number of Connected Components in an Undirected Graph - LeetCode</t>
+  </si>
+  <si>
+    <t>Same solution as Redundant conneciton.
+But we will not return the edge when parents of both nodes in edge are same.
+We will go through all the edges in given array.
+After which we will call find parent method for all the childs from 0 to n. and add the result to set.
+return set.size(). each connected component will have same parent, so number of unique parents mean number of components</t>
+  </si>
+  <si>
+    <t>Same as redundant connection</t>
+  </si>
+  <si>
+    <t>Graph Valid Tree - LeetCode</t>
+  </si>
+  <si>
+    <t>A valid tree is a graph where all the nodes are connected and ther are no cycles.
+Solution is combination od redundant connection and number of connected components.
+In this sultion we  will return false if parents of both the nodes are same. Means they are in same component and create the cycle.
+After going though all the edges in given array. we will find parent for all the nodes fron 0 to n. if there are multiple parents the return false else true.</t>
+  </si>
+  <si>
+    <t>Word Ladder - LeetCode</t>
+  </si>
+  <si>
+    <t>We will use BFS to solve this.
+Create a set from given work list.
+Create a queue of string. Add the begin string to it.
+Create a  valiable to keep trak of lenght. 
+While queue is not empty. 
+We will iterate over the queue for queue.size() times.
+if the word == end word return lenght;
+else we will replace every character from the word with a-z. and if the new work is present in the word list we will add it to the queue. Remove that work from the set so it does not get added again. after one iteration over queue.size() increment the lenght by 1.</t>
+  </si>
+  <si>
+    <t>If end strign is not in the given word list return 0;
+when replacing caharacters in the word with a-z keep track of original character we are replacing.
+Add the original character back after replacement.
+We can solve brom both the ends for lower execution time.</t>
+  </si>
+  <si>
+    <t>Climbing Stairs - LeetCode</t>
+  </si>
+  <si>
+    <t>Min Cost Climbing Stairs - LeetCode</t>
+  </si>
+  <si>
+    <t>Result depends on the calculation of privous value.
+For e.g. if you want to calculate for n=10 you have to calculate n=9+n=8, n=8+n=7, n=7+n=6 and so on.
+At each we have 2 options take 1 step or take 2 steps. So the result is steps(n-1)+steps(n-2).
+We can use recursive steps method get the result and cach the result for each step and store in the cache or dp if the value is not -1 we can return the value.
+else we can calulate it as above.
+Another way to solve this is to iterate over the array from 0 to steps.
+at each step the result is dp[i-1]+dp[i-2].
+more optimized way is to remove the dp and only keep track of prev 1 and prev 2.
+This problem is same as fibonacci series</t>
+  </si>
+  <si>
+    <t>Result depends on the calculation of privious value.
+We can recursively call the method and check the minimum(step+1, step+2) store the value for that step in a dp arrays. if the index is &gt;= given array.lenght return 0.
+That means we have to start building theresult.
+Iterative approach.
+We will start from th elast step.
+set the min value for the last and 2nd last step as the cost of that step. now start calculating the result in reverse order. at each step we calculate the cost[step] + min(step+1, step +2). At last return min(step1, step1) because we can start from 0th or 1st step.
+We can refactor the code and remove dp array keep track of prev1 and prev 2 and reduce space complexity.</t>
+  </si>
+  <si>
+    <t>House Robber - LeetCode</t>
+  </si>
+  <si>
+    <t>Result depends on the calculation of the future values.
+To calculate the max at current house we have to find out if we can max out on the robbed money by robbing the current house. If we do so then we have to skip the next house and rob house+2. or we can skip current house or rob next house.
+we can do this recursively and start building the result and sroting in cache when the index is out of bound. in this case we return 0.
+To solve this iteratively. we start from th elast house. in the cache for the last index we can have the value as the original. in the 2nd last position we can have value max(2nd last, last ).
+now we can start calculating the result backwards.
+at each index we we calculate the result like this. dp[i] = max(dp[i]+ dp[i+2], dp[i+1]);
+We can refactor the code and remove dp array keep track of prev1 and prev 2 and reduce space complexity.</t>
+  </si>
+  <si>
+    <t>0=0
+1=1
+2=2
+3=3
+these are the base cases and should be stored in the cache or dp
+we can remvoe the caching or dp because at each step we need only 2 values dp[i-1], dp[i-2]</t>
+  </si>
+  <si>
+    <t>we can set min value for the last and 2nd last step as the cost of that step
+because we can pay the value at that step and each at top. No extra cost to pay
+we can remove the dp because we need only 2 values at any step, step+1, step+2.</t>
+  </si>
+  <si>
+    <t>we can remove the dp because we need only 2 values at any step, dp[i+2], dp[i+1]</t>
+  </si>
+  <si>
+    <t>House Robber II - LeetCode</t>
+  </si>
+  <si>
+    <t>The base logic to solve this problem is same as house robber 1.
+in this problem we can calcualte the result by using same logic 2 times.
+Since the houses are in circle. If we rob first house then we cannot rob last and if we do not rob 1st house then we can rob last house.
+With this logic we can calculate the max robbed money 2 time with the star and end index as 0 to lenght-2, and 1 to length-1
+Like house robber 1 we can calculate using recursive or iterative approach.
+return the max of this 2 calculations.</t>
+  </si>
+  <si>
+    <t>Longest Palindromic Substring - LeetCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We will iterate over each index of the given string. 
+At each index we have to check for the substring 2 times. 
+One with l and r == i, and one with l == i and r == i+1. at each step check if the length r-l+1 is greater than the res. If yes update. update the pointers and compare while charAt(l)==charAt(r). </t>
+  </si>
+  <si>
+    <t>Why 2 we have to check 2 times. Be Strings "a" and "aa" odd length and even length both are palindromes. For both the while loops make sure that you are adding the constains such that indexes are with in the bounds.</t>
+  </si>
+  <si>
+    <t>Palindromic Substrings - LeetCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logic will be same as longest panlindromic substring. Instead of comparing the length update counter by 1 is </t>
+  </si>
+  <si>
+    <t>Decode Ways - LeetCode</t>
+  </si>
+  <si>
+    <t>Result depends on the calculation of the future values.
+At given index the we have 2 choices decode 1 character or decode 2 characters.
+Case 1 decode 1 char. If the char is 0 we cannot decde it as it not a valid input else we can decode. Call the recursive method with index+1.
+case 2. decode 2 chars. here is the 1st char is 1 then decode the 2 chars togeter or if 1st char is 2 then check if the 2nd char is  o to 6 only then decode else do not deocde. the result for the current index will be addition of case1 result + case 2 result. we can save the result in case. When we reach the end of the string we return 1.(as it is one way to decode) and start building up the result.
+for better performance and clean code we can calculate the numers by subracting -'0' from the cirrent char
+s.charAt(index) - '0'; currNumber * 10 + s.charAt(index + 1) - '0';</t>
+  </si>
+  <si>
+    <t>there are few edge cases to look for. 
+If the index == length return 1. (success case we can decode the stirng)
+if charAt(index) = '0' return 0;
+To decode 2 character there must be 2 characters in th estring available. So before trying to decode 2 characters check if index is within the bonds.</t>
+  </si>
+  <si>
+    <t>Coin Change - LeetCode</t>
+  </si>
+  <si>
+    <t>Result depends on the previous values.
+To calculate minimun coins to amount 10 we have to get the minimun coins for 9,8,7…..
+This solution is easy with iterative approach.
+At each index we calculate we iterate over given coins array. If the coin &lt;= I we calculate house much coins are need using min(1+dp[i-coin], dp[i]).
+at last re return dp[target];</t>
+  </si>
+  <si>
+    <t>while iteraing overs coins array in inner for loop make sure that you are adding condition coin&lt;=I
+other wise we will get index out of bounds.</t>
+  </si>
+  <si>
+    <t>Maximum Product Subarray - LeetCode</t>
+  </si>
+  <si>
+    <t>No dp or recursion needed can be silved by iteration.
+We will iterate 2 times from start to end and end to start. And multiply the numbers togeter
+We will keep track of max. and if the the number is 0 we reset to 1.</t>
+  </si>
+  <si>
+    <t>Word Break - LeetCode</t>
+  </si>
+  <si>
+    <t>can be solved using recursion and iteration combined.
+we will write a recursive method. 
+We will iterate over each character and check if the substring/word exists in the the dictionary.
+If yes then we call the recursive method again with updated pointers.
+We will return true immidiately if the result of the both operations above (exist, recursive method call) is true else we will continue with the iteration.</t>
+  </si>
+  <si>
+    <t>return true only when the index is string.length.
+We will use Boolean (wrapper class) dp array to store the result of each index. As there can be 3 possible values.
+True means word break is success. False means work break is not success for given index.
+And null means yet to be calculate.
+We can use boolean dp array as  well but it will ake the logic a little bit hard to understand at first.</t>
+  </si>
+  <si>
+    <t>Longest Increasing Subsequence - LeetCode</t>
+  </si>
+  <si>
+    <t>We will use iterative solutions for this to solve.
+We initialize the dp array with default values as 1. as each number is sequence of max length 1 in itself.
+We will have nested for loop. For each index. We will have inner for loop which iterates till i-1.
+if the inner foor loop number is less than the outer for loop number we will update the dp[i] = dp[j]+1; for each inner iteration we will keep track of max length. return max length</t>
+  </si>
+  <si>
+    <t>Partition Equal Subset Sum - LeetCode</t>
+  </si>
+  <si>
+    <t>To find if we can partition the given array in equal sums. We have to find if we can find sum = total/2 in the given array.
+To do that we can iterate over each number in given array. For number number we can have inner for loop over dp array in rever order till number. if the we dp[i-number] == true then set j = true;
+return dp[total/2].</t>
+  </si>
+  <si>
+    <t>we have to find total.
+Dp array is boolean array which will track if the index(sum) can be reached with the given number. Initial condition dp[0] = true;
+we iterate over dp array to find what all possible sums can be formed with given numbers array. 
+We iterate in the reverse order so that we dont calculate the sum using same number again(repeated numbers in given array are to considered as distinct and should be used only once.) suppose we have 1 in the given numbers array. if start from 0 then all the values in the dp array will be true. as 1-0, 2-1, 3-2 will all be true.
+since 1+5 and 5+1 = 6, sequence does not matter we will get the same result.</t>
+  </si>
+  <si>
+    <t>Unique Paths - LeetCode</t>
+  </si>
+  <si>
+    <t>To get to each cell we have 2 choices either from above or from left. With this logic we can solve this problem.
+For the top most row and left most column the values will be one as there is only one to get to them.
+For the rows &gt;=1 and column &gt;= 1 we can have a nester for loop and the values for them can be calulated like dp[i][j] = dp[i-1][j] + dp[i][j-1]. this means that
+number of ways to get to any cell in grid = number of ways to get to cell above it + numbers ways to get to cell on left of it.</t>
+  </si>
+  <si>
+    <t>Initial conditions = For the top most row and left most column the values will be one as there is only one to get to them.</t>
+  </si>
+  <si>
+    <t>Longest Common Subsequence - LeetCode</t>
+  </si>
+  <si>
+    <t>this can be solved by using the dp on the index of both the string to keep track of longest se quence will that point.
+Create a grid of of dimentions s1.lenght+1 and s2.length+1. because starting the the iterations the index starts before 0.
+the top most row and left most column values will  be 0, as they indicate index before 0.
+now we start the iterations on the grid from 1. for each cell we will check if the char at the index i == chat at index j.
+if yes then the value dp[i][j] = 1+ dp[i-1][j-1].(we have matiching character and sequence ount can be incremented.)
+else value dp[i][j] = max(value at top, value at left) (the character does not match and sequence will remain same)</t>
+  </si>
+  <si>
+    <t>Initial condition = the top most row and left most column values will  be 0, as they indicate index before 0.</t>
+  </si>
+  <si>
+    <t>Best Time to Buy and Sell Stock with Cooldown - LeetCode</t>
+  </si>
+  <si>
+    <t>This provlem falls under state machine dp. Meaning that at each step state changes and and depending on the state operation changes.
+Eg if we buy a stock then we must sell it. And if we sell it we cannot buy for one day. And sicne the state changes the operations also changes for that state.
+for any given day/index we have 2 options buy or sell. So we can have a dp array to cache the results dp[prices.length][2]. column 0 for buy and column 1 for sell.
+initializae the value as -1 so that we know which result is already computed.
+initialize a pointer to keep track of the profits. When we buy a stock we subract the number becuase we are putting money out of our pocket to buy. and if we are selling the stock we will add the number.
+We will use recursion as the choices are limited and make the code understandable.
+for the given index we will have 2 states. buy or sell
+if the state is buy then 
+1. we can buy the stock subract the price increase the index and change the state to sell.
+2. we can skip to buy the current stock and move ahead. increase the index and keep the state same.
+if the same is sell then
+1. we can sell the stock add the price incease the index by 2 (because of 1 day cool down) and change the state to buy.
+2. we can decide to not sell the stock increase the index by 1. keep the state same.
+At each index we store the max of both the choices result in dp array. if  the result is already calculated value != -1 then return the result immidiate before calculating again.</t>
+  </si>
+  <si>
+    <t>if the index is out of bounds return 0.
+This algorithm falls under state machine dp. Beucase at each step the state changes and we are breaking down bigger problem in smaller problem and caching the result.</t>
+  </si>
+  <si>
+    <t>Coin Change II - LeetCode</t>
+  </si>
+  <si>
+    <t>The logic to solve this problem is reverse of the coin change 1. problem
+Because in this problem 1+2 and 2+1 are considered as same.
+So to avoide duplication once we use a coin we can never use it again to avoid duplication.
+intial condition will be dp[0] = 1 as we can have 0 value in one way.
+So we will iterate over given coins array in outer for loop (so that each coin is used only once.)
+inside for each value from coin to target  the dp[i] = dp[i] + dp[i-candidate].</t>
+  </si>
+  <si>
+    <t>Target Sum - LeetCode</t>
+  </si>
+  <si>
+    <t>At each position we have a choise if we want to add the number or we want to sumbract the number.
+We will  use recursion for this. At each step we will call the resursive method 2 time by adding current number or by subracting current number. the asnwer is addition of both.
+If the sum == target and index == array.length that means we have found one possible way so we return one. 
+if the index is out of bound return 0. (not the right way).</t>
+  </si>
+  <si>
+    <t>Since we are subtracting the values it is posiible to have the sum as -ve. Value. 
+So we can get the sum up to -sum to +sum. So the dp array we create will be dp[idx][2*total+1].
+This will  avoid null pointer excpetion. While storing the values in dp or getting the values from dp fetch it by adjusting the values like dp[idx][totalSum+currentSum]</t>
+  </si>
+  <si>
+    <t>Interleaving String - LeetCode</t>
+  </si>
+  <si>
+    <t>this problem can be solved by combination of recursion and iterations
+We can have dp array of size s1.length and s2.length. We will start from indexes 0, 0, 0 in the recusrive method, at index if the character of any 2 strings s1, s2 == character in the string s3. we call the recursive method again awitht the updated pointers.
+if we reach end of the all the strings we return true immidiately.
+else return false</t>
+  </si>
+  <si>
+    <t>Check the indexes before cehcking for equality of characters to avoid num pointer exception. 
+Return 1 only if all the index are equal to the length of reqpective string.
+To save time(not reduce the time complexity). After comparing s1 and s3 if the result is true return true immidiately. continue with comparing s2 and s3 only if the result of first is false.
+Use Boolean[] for better clean code. true means we have found the result. false means at tgiven index the result cannot be calculated. and null means reutn to be calculated.
+we can refactor the code and use boolean[] but the code becomes less readable.</t>
+  </si>
+  <si>
+    <t>Longest Increasing Path in a Matrix - LeetCode</t>
+  </si>
+  <si>
+    <t>Create a 2d DP Array. Iterate over each cell, for each cell we will calculate the increasing sequence in all 4 directions.
+Febore calling the recursive method we weill check if the values are in bounds and next element is greater then current.
+Final result will be 1+ max(all  direction). store the result in dp array and track max.
+result result if dp cell value is not 0</t>
+  </si>
+  <si>
+    <t>Distinct Subsequences - LeetCode</t>
+  </si>
+  <si>
+    <t>Create a 2d DP array. Start 2 indexes for 2 string. 
+If characters at 2 indexes are same then we can either take the character or we can skip it.
+If we decide to take it. Then call recusrive methos by incrementing the indexes. If we decide to skip it then increment the index of s.
+else if both the chars are different then increment the index of s and call the method again.
+at each step store the result in dp array.
+if value is not -1 return the value</t>
+  </si>
+  <si>
+    <t>return 1 if index of t == t.lenght that means we have one subsecquence.
+Return 0 if index if s == s.length that we have reached the end og string s but bot able to find a subsequence.</t>
+  </si>
+  <si>
+    <t>Edit Distance - LeetCode</t>
+  </si>
+  <si>
+    <t>At each step answer depedns on 2 things, if the characters are equal. If yes. Then we move both pointers one pos.
+if chars are different then we have 3 different options. 
+Insert :- we insert  a char before. Idx1 remains same idx2 moves ahead.
+Delete :- idx1 moves ahead, and idx2 remains same.
+repalce:- move both the pointers ahead.
+based on the edge cases we can build the answers in bottom up format.
+if chars are same then dp[i][j] = dp[i+1][j+1]
+if not then dp[i][j] = 1+ max(dp[i+1][j+1], dp[i+1][j], dp[i][j+1])
+since at each modifications counts as one operation we add 1 to min value</t>
+  </si>
+  <si>
+    <t>we can build the edge cases on this exampl. If s = "" anf t = "hello" then we will need 5 steps.
+So to build the initial bases case in DP array. We will use this logic.</t>
+  </si>
+  <si>
+    <t>Burst Balloons - LeetCode</t>
+  </si>
+  <si>
+    <t>Complete explanation cannot be written here as it is big and complex.
+Be basic Idea to solve this problem is. Instead of calculating what will happen if we burst the bolloon first.
+We can check what will happen if we burst the balloons last.
+By using this technique we can store the results in 2d dp array.
+complete exmplaination in youtube video :- https://www.youtube.com/watch?v=VFskby7lUbw&amp;t=1016s</t>
+  </si>
+  <si>
+    <t>Check the video</t>
+  </si>
+  <si>
+    <t>Regular Expression Matching - LeetCode</t>
+  </si>
+  <si>
+    <t>We can solve this question by checking the next character in the pattern p.
+first we will check if the character is matched. The condition will be.
+If index is in bounds and characters are same or pattern has "."
+now we will check if next char in pattern *. is yes then we have 2 options. we can skip the * and move ahead.
+so call the recursive method with idx1, idx2+2.
+or we can take that character and callt he recusive method with index idx+1, idx2.
+Else if character is matched we move both the pointers ahead. 
+Store the reuslt in dp, use Boolean array as dp. return the value if != null</t>
+  </si>
+  <si>
+    <t>return true only if both the indexes reach end.
+Return false only if j reaches end. Do add logic to return false if s reached because it is posible that s might reach end. But p has * patterns left. So it will be a valid string.</t>
+  </si>
+  <si>
+    <t>Maximum Subarray - LeetCode</t>
+  </si>
+  <si>
+    <t>negative values does not contribute to the Max value.
+Since -ve calues does not contrivbute to max value any sub array whose sum is -ve also does not contribute to the max value.
+So the solution is, iterate over the array keep track of max sum, and if currsum is -ve reset the curr sum to 0;</t>
+  </si>
+  <si>
+    <t>Jump Game - LeetCode</t>
+  </si>
+  <si>
+    <t>instead of thinking how far can we reach from starting point. We can try to find if we can reach target from privous point.
+Iterate over the array, if the target is within range update the target to current the current index.</t>
+  </si>
+  <si>
+    <t>Jump Game II - LeetCode</t>
+  </si>
+  <si>
+    <t>This is similar to BFS, we have to find out what is the max that we can reach from the given index.
+Then repeat this step till you reach the end. Number of steps is the answer.</t>
+  </si>
+  <si>
+    <t>Gas Station - LeetCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If the difference between cost to reach next station and refill at current station is less than 0. that means we cannot reach the next station to update the answer to next index.
+Also is total difference of all the indexes is &lt; 0 we cannot complete the circle, 
+Iterate over the array calculate the difference, maintain 2 variables, currTotal and total, keep updating both the pointers. if at any point currtotal is &lt; 0 update the res to next pointer. after iteration is complete. check if total &lt; 0 is yes, then return -1. that means we cannot complete the circle </t>
+  </si>
+  <si>
+    <t>Hand of Straights - LeetCode</t>
+  </si>
+  <si>
+    <t>Since we need the consecutive numbers in increasing order. We can sort the Array.
+Iterae over the array. Anf for each index check if we can find a consecutive number. 
+Logic to find consecutive numbers will be like folloing. 
+iterate over the given array from the current index till the end. if the number at the index if &gt; n+1 return false, that means we could not find consecutive numebrs.
+if number ==  n || -1. continue. else update the value at index as -1, increment the group counter. update number. return true if the group is found</t>
+  </si>
+  <si>
+    <t>Merge Triplets to Form Target Triplet - LeetCode</t>
+  </si>
+  <si>
+    <t>Since we have check inf the triplet can be found. We just have to check if there esist such a triplet  where the value at given index is same the target triplet, and other 2 values are less than or eqal to values in the target triplet.
+Once with find all 3, return true;</t>
+  </si>
+  <si>
+    <t>Partition Labels - LeetCode</t>
+  </si>
+  <si>
+    <t>Iterate over the strign to find the last index of every character, store it in array, 
+Create an list to store result, and a variable to store the start index. 
+While start index is &lt; than string length, we keep track of last index for the character at start index. 
+from index start index till end index. for each character update the last index. after the loop is completed update result list. update the start index = lastIndex+1;</t>
+  </si>
+  <si>
+    <t>Valid Parenthesis String - LeetCode</t>
+  </si>
+  <si>
+    <t>Instead of pushing ( * to the stacks, we will push the indexes. So that we can find matching pair in the while loop</t>
+  </si>
+  <si>
+    <t>This can be easily solved with stack, no need of greedy.
+We will use 2 stacks, one for opening brackets and one for *.
+For each character in given string. We will update the stack if its ( or *. If its ) we will check if bracket stack is non empty is yes then we pop one bracket.
+If its empty we will check if * stack is non empty if yes we pop 1 *. else we return false, as it is not a valid paranthesis.
+After this loop it is possible that we there may be  some ( left in the stack. we have to iterate over then as well while stack is non empty
+if the index at the top of * stack is &lt; index of (. return false. if not we pop from both the stacks.
+after the loop is executed completely that means all ( and ) are matched correctly. Now only * may be remaining. and since the star can have "" value, we can ignore them so the parathesis is valis and we can return true</t>
+  </si>
+  <si>
+    <t>leetcode.com/problems/meeting-rooms/</t>
+  </si>
+  <si>
+    <t>Sort the given array based on the start time.
+For each interval is the start time of current interval is less than end time of prev interval return false.</t>
+  </si>
+  <si>
+    <t>Make sure that start time is less, is the start and end time is same
+then it is not overlapping interval</t>
+  </si>
+  <si>
+    <t>Meeting Rooms II - LeetCode</t>
+  </si>
+  <si>
+    <t>Create 2 arrays, start and end time,
+sort the 2 arrays,
+create 2 pointers for 2 arrays s and e, and a variable to store the count
+While s is less than s.length.
+If start is &lt; end then increment the counter, and move the s pointer to next pos, else decrement the counter and move the e pointer to next pos
+at every interation store the max counter in res.</t>
+  </si>
+  <si>
+    <t>why s&lt; s.length? because we care only about when the neeting starts.</t>
+  </si>
+  <si>
+    <t>Insert Interval - LeetCode</t>
+  </si>
+  <si>
+    <t>iterate over the given array.there can be any one of the 3 conditions posible,
+if start time of new interval is greater than end time of current interval. Then we will add the current interval.
+Else if end time of newInterval is &lt; start time of current interval then we add the new interval and add the remaining intervals to the results set and return.
+else (start time of end time lie in between the intervals) then we merge the interval, we take start time as min of both and end time as max of both.but we do not add that interval to the result set yet, because ther may  be a posibility that we will need to merge the next interval as well.</t>
+  </si>
+  <si>
+    <t>We should not add the merged interval because there is a possibility that we will need tot merge the next interval as well</t>
+  </si>
+  <si>
+    <t>Merge Intervals - LeetCode</t>
+  </si>
+  <si>
+    <t>we will initialize the previous interval as the 1st element of the array.
+Iterate over the given array and if the start time of current interval is less than or equal end time of the privious interval we merge the interval. And assign the value to privous interval
+Else we add the privous interval to the list and assign current interval to the privous interval.</t>
+  </si>
+  <si>
+    <t>Do not add immidiately after merging, we may need to merge again</t>
+  </si>
+  <si>
+    <t>Non-overlapping Intervals - LeetCode</t>
+  </si>
+  <si>
+    <t>The factor that decides the minimum intevals to be removed is the end time.
+Interval having the longest end time will possibly overlap the most other intervals and should be removed
+Sort the given array based on the start times. Create a variable to keep track of the end point.
+iterate over the array. if start time of the current element is less than the end time of the privous element. then we increment the counter and update the end time variable with the min of current end time and priv end time, 
+else update the privious end time with the current interval end time</t>
+  </si>
+  <si>
+    <t>Why min when updating priv end time. Because we must remove the interval with longest end time.
+So by updating the priv interval with min we technically remove the interval with longest end time</t>
+  </si>
+  <si>
+    <t>Rotate Image - LeetCode</t>
+  </si>
+  <si>
+    <t>Easiliest way to do the create new matrix convert row to column then update the values in original matrix.
+But the problem says do not use new matrix.
+We can draw a diagonal from top left to bottom right. We will get 2 triangles.
+We can swap the values in these 2 triangles, like matrix[i][j] ==  matrix[j][i].
+then in the 2nd loop, we can swap the values  horizontally,</t>
+  </si>
+  <si>
+    <t>Spiral Matrix - LeetCode</t>
+  </si>
+  <si>
+    <t>We will have 4 pointers, left right, top and bottom, for each direction we will have a loop,
+1st :- left to right on top row,
+2nd :- top to bottom right column.
+3rd :-right to let on bottom row
+4th :- bottom to top on left column 
+After each loop we will the the pointers,
+After the first 2 loops we will check if left == right or top == bottom.
+if yes return</t>
+  </si>
+  <si>
+    <t>Why to check if check if left == right or top == bottom.
+Because for column matrix or row matrix, if we use 3rd and 4th lopp with out checking this conditiont hen the values will get reapeated.</t>
+  </si>
+  <si>
+    <t>Set Matrix Zeroes - LeetCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create 2 sets one for column and one for row.
+Iterate over the matrix if the value is 0, add the row and column index to the respective set.
+Now iterate over the sets. And set the values in respective column and row to 0; 
+Another faster way:-
+instead of using set. we can use the matrix itself to store the values which needs to be 0. Because entire row and entire column needs to be updated with 0. if we update the 0 in the first columns or first row. we can update values with zero later easily using matrix[i][0] == 0 || matrix[0][j] == 0;
+Before this we have to check if the 0 exist in first column or first row. And store it in boolean value. After the entire operation is done, then we can set the 0 in first row or first column based on the boolean values </t>
+  </si>
+  <si>
+    <t>Happy Number - LeetCode</t>
+  </si>
+  <si>
+    <t>We have to find the loop. So we can use rabit and hare algorithm.
+we will have 2 variables slow and fast, calculate the sum for slow once.
+Calculate the sum for fast twice for fast.
+Now we run loop,
+while slow != 1 or fast != 1 or slow != fast (1 is the correct answer that means number is happy number, is slow == fast then we get a loop number is not happy number) we update the slow and fast.
+after the while lop, check if any of the variables is 1. is yes return true, else fasle</t>
+  </si>
+  <si>
+    <t>Plus One - LeetCode</t>
+  </si>
+  <si>
+    <t>Start wih carry as 1, iterate over the array from right to left and the carry to the number at that index.
+Update value as sum%10 carry as sum/10;
+after the loop, cehck if the carry is &gt; 0 if yes,create new array, add carry in the beginning add rest of values after and return new array. else return the original array</t>
+  </si>
+  <si>
+    <t>Pow(x, n) - LeetCode</t>
+  </si>
+  <si>
+    <t>We can use divide and conquor method, 
+if we have to find pow(x, y) instead of calculating. x.x.x….. (y times,) we can calulate x.x.x.x….(y/2 times) and multiply that 2 times.</t>
+  </si>
+  <si>
+    <t>lot of base conditions.
+If n == 0 return 1; 
+if n &lt;0 then return 1/answer; (because 2 pow -2 is same as 1/(2 pow 2)) (make the power +ve) 
+else reutrn answer;  
+while calculating the power. After getting the half. If the power % 2 is 1 then return half*half*x (because in java 5/2 is 2).
+else return half*half</t>
+  </si>
+  <si>
+    <t>Multiply Strings - LeetCode</t>
+  </si>
+  <si>
+    <t>Write the logic to mimic the multiplication we do on paper.</t>
+  </si>
+  <si>
+    <t>When doing on paper multiplication. We multiply from right to left. While coding it will be difficult to write so reverse the input string,
+This will build the result in resverse manner then, reverse the result for actual result.
+When multiplying integers at indexes make sure that the result array is updated correctly. since there may be non zero values in the result array at any given point, make sure that when calculating the sum you add the exisiting value to the multiplication. 
+Update the index with sum%10. and update the index+1(carry) with (sum/10 + value at that index). 
+For any given numbers the length of result will be addition of length of both the numebrs. eg:- multiplication of 2 digit numbers will result into the max length of 4 digits. so when calculating the result you have to update it at the index i+j.
+There may be leading zeros after the multiplication is completed. Make sure to remove those</t>
+  </si>
+  <si>
+    <t>Detect Squares - LeetCode</t>
+  </si>
+  <si>
+    <t>You will need a list to store all the points and Map to store the freq, 
+the key of the map will be x + '@' + y. 
+To find the count of the squares, instead of finding 3 valid points. We can find a valid diagonal point, and then check if other 2 points exist. If yes then increment the count. Since the duplicate points will be considers as separate points. when increment the count we have to multiply the freqency of the  3 other points.</t>
+  </si>
+  <si>
+    <t>Make sure the same point is not considers when counting the squares.
+If the point is same or the |x| and |y| distance is not same. Do not consider that point.</t>
+  </si>
+  <si>
+    <t>Single Number - LeetCode</t>
+  </si>
+  <si>
+    <t>Use XOR on all the elements, and return the result
+Why XOR? XOR returns 0 when the the bits are same. So for duplicate numbers bits are same. So the result cancel outs each other.
+Also the sequence of XOR does not matter.</t>
+  </si>
+  <si>
+    <t>Number of 1 Bits - LeetCode</t>
+  </si>
+  <si>
+    <t>Mod the number by 2 if res == 1 increment the count.
+Then move the number to right by 1 bit.</t>
+  </si>
+  <si>
+    <t>Counting Bits - LeetCode</t>
+  </si>
+  <si>
+    <t>The logic to solve this is that, the privious bits remain the same. The only bit that changes is 1st bit.
+Also the most significant bit changes after every power of 2. 
+So we can calculate the result of new number by using the the result of privous number +1.
+you can keep track of offset and update it accordingly.</t>
+  </si>
+  <si>
+    <t>for 0 and 1 answer remains 0 and 1. 
+so start from 2 onwards and offset as one.</t>
+  </si>
+  <si>
+    <t>Reverse Bits - LeetCode</t>
+  </si>
+  <si>
+    <t>To get the least significant bit. We can % the number by 2 or  logic &amp; the number with 1.  
+we can left shit the result by 1 bit and  add the least significant bit.
+Update move the number to one bit right</t>
+  </si>
+  <si>
+    <t>Missing Number - LeetCode</t>
+  </si>
+  <si>
+    <t>we can solve this question by using XOR.
+Iterate from 1 to n for each number use a XOR. 
+Now iterate over the given array and use the XOR.
+Return the result
+To find the sum of n numerbs user n(n+1)/2.
+now subtract he numbers from given array.
+Reutrn the result</t>
+  </si>
+  <si>
+    <t>Reverse Integer - LeetCode</t>
+  </si>
+  <si>
+    <t>You can easily calculate the reverse by using reverseInt*10 + int%10
+But the reversed int can overflow the value of int which is 32 bits.
+So afte reversing the number check if reverse is also true. By following logic
+            int newInt = reversedInt*10 + x%10;
+            if((newInt - x%10)/10 != reversedInt) return 0;
+update the number</t>
+  </si>
+  <si>
+    <t>The reversed number can overflow the int 32 bit range</t>
+  </si>
+  <si>
+    <t>Reconstruct Itinerary - LeetCode</t>
+  </si>
+  <si>
+    <t>None edege case but some clarification.
+Why this logic works? Because we build the Itenerary in reverse order rather than in straight oder where we may not be able to  cover all the branches of the graph if the cycle does not exist.
+When using while loop we poll the element. and since we are not "Iterating" over the queue we can remove/poll the element easily. Also when the call reched the same apirport since we hgave polled the first airport the next call will be made with new path automatically so that we dont have to keep track of visited and non visited apirports.</t>
+  </si>
+  <si>
+    <t>Min Cost to Connect All Points - LeetCode</t>
+  </si>
+  <si>
+    <t>Create adjececncy list for all the apirports usign a priority queue since we will ge the apirports in lexical order (sorted based on characters and length)
+Then we do a post order DFS
+The logic behind the post order DFS is that we will go down the dfs but add the current node to result "after" adding neighbouring dfs result. its like building the itenerary but in reserse order
+While the PQ is not empty we will poll the 1st element and call the recusrive method again.
+after the while loop when the PQ is empty. we will add the current apirport to the res in "first" position.
+This is somewhat similar to Topological sort.</t>
+  </si>
+  <si>
+    <t>Network Delay Time - LeetCode</t>
+  </si>
+  <si>
+    <t>start visited points count with 1 and mark the index 0 as true as we are aleady starting the first element in the given array.
+This algorith works even if we start at any point</t>
+  </si>
+  <si>
+    <t>This is similar to Dijkstra's Algorithm. This problem is MSP problem. minimum spanning tree.
+We will create adjecency list by connecting all the points with each other.
+The neighbous in this adjecency list will be a int[] of size 2. the first index will be the index of the point in the given array.
+and 2nd index will be the weight/dist between them.
+We initialize the priority queue which sorts based on the min distance.
+we add the first element from the given array to the queue.
+We keep track of visited points count and visited indexes.
+Now we run a while loop. visited points count &lt;= given array.length 
+Poll the element from the queue. Since the queue is sorted based on the dist. next closest point will be at the top of the queue(min Heap). check if the index is aleady visited if yes contnue. mark it in visited, increment the count, add the distance to the result. Now we add all its neightours to the priority queue if the neighbour index is not already visited. (we can add all the ements regardless of visited or not time complexity does not change as we are already checking if the point is visted. To keep the run time low we do not add aleady visited points as Priority queue runs in N log N time ).</t>
+  </si>
+  <si>
+    <t>We do not skip if the node is already visited be cause the new path may be with the smallest weight.</t>
+  </si>
+  <si>
+    <t>Swim in Rising Water - LeetCode</t>
+  </si>
+  <si>
+    <t>The base logic to solve this problem is that we have to weight till the time is &gt;= the value of the cell.
+Alternatively instead of waiting for the timer. We can set the time to the 1st element in the queue.
+Create a priority queue which sorts the nodes based on the value of the cell.
+the node will be of 3 values row column index.
+Initialize a variable to keep track of time. 
+Initialize a visited array.
+add the 1st cell to the queue.
+now we run the while loop till the queue is not empty.
+We poll the element and update the max value of the timer between current and node timer.
+if the end cell is reached return the result.
+now we add the neighbours to the queue. if they are in bound and not already visited. when adding the element to the queue mark the cell as visited</t>
+  </si>
+  <si>
+    <t>Alien Dictionary - LeetCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We have to create a adjecency list from the given array of the string.
+Logic to create adjecency list. 
+We iterate over 2 string at a time. i and i-1.
+start a index 0 iterate over both the strign with same index. If the both the chars are same continue. else we add then to adjecency list. 
+since the given arrayis already sorted as per the alien dictionary (lexical sort). s2.charAt(idx) comes after s1.charAt(idx) as per the alphabetical order of alien dictionary. That means s2.charAt(idx) depends on s1.charAt(idx). That means in adjecency list key will be s2.charAt(idx) and the neighbours will be s1.charAt(idx)
+Now we run the post order DFS. This logic works even if we start at any point.
+Since in the adjecency list key is the last element and neighbours is the privious elements(as oer the alphabetical oder of alien dictionary). when adding to the result we add last. 
+To run the post order DFS we need a Visited array to mark the visited characters. use Boolean so that we can have null true and false. Reffer the code for detailed implementation of Post Order DFS </t>
+  </si>
+  <si>
+    <t>While comparing 2 strings.
+Create the entry for all the characters present in the given all the given strings.
+check if the initial part of the s1 and s2 is same (from 0 to min(s1.length, s2 length))&amp;  s1 length &gt; s2 length if yes then it is not a valid dictionary and return empty string.
+when post order DFS we can start from any point and still the result is correct because this is topological sort. and the sequecnce may change. It is correct as long as dependency comes before dependent.</t>
+  </si>
+  <si>
+    <t>Cheapest Flights Within K Stops - LeetCode</t>
+  </si>
+  <si>
+    <t>Why the sequence when processing is imp, dst does not contribute to the jump.
+We do not want to process is the jumps are greater than K.
+we update the min cost only when both of these conditions are met.
+Why to have a copy array and  check if the current edge cost + cost of src node from original array is &lt; cost of dst node in copy array. because basically we have to go through all the out going edges from all the nodes we have visited so far and find the minimum to reach the dst. While do ing to it is possible to update the values with incorrect data as we will be updating same cost array multiple time. To avoid this we create a array copy. Also while doing so it is possible that we have already found a min to reach dst and we found a new min to we have to check in the copy array not original</t>
+  </si>
+  <si>
+    <t>This is Dijkstra's Algorithm.
+We create adjecency list based on the given input.
+The neighbours will be int[] of size 2, node and weight, 
+we create priority queue which sorts based on the min weight.
+Create the res array which hold the min weight to reach the node.
+initialize it with Max value.
+Mark the start node weight as 0 as we are starting from it and weight is 0.
+We add the given node to the queue with weight as 0. becasue we are alaready at that point and we dont need anything to reach it.
+Now we run the while loop till the queue is empty.
+poll the first elemnt from the queue(Min heap). check if the weight is less than the weight in the stored res array. is yes update it else continue.
+ now we add the neighbours to the queue. if the weight to reach the neighbour + current weight is &lt; the weight in the stored res array we add it to the queue else not.
+After the while loop is finished iterate over the res array and find the math value.
+while iterating if any of the value is max value then we return -1 as that node is not connected to the graph and we were not able to reach it.</t>
+  </si>
+  <si>
+    <t>This problem can be solved with Dijkstra's Algorithm as well as bellmon ford algorith as well.
+Solve this problem with Dijkstra's Algorithm:-
+ we are allowed to update the min weight is the weight is less than current also if the numebr of steps are different.
+So we need 2d array to store the results. new int[nodes][k+2]. fill it with mx values and Initialize the [src][0] as 0 as it is the starting point. 
+Why k +2 becasue we will start from src and end at dst and src and dst are not considered as jumps. 
+Now we do the Dijkstra's Algorithm.
+There should be 3 values for a ndoe in priority queue node, weight and jumps.
+when processing a entry from the priority queue check in this order 
+first check if the current node is dst if yes return current cost.
+seconds check if the the k is greater than k is res continue.
+min cost. 
+After the queue is empty return -1 because we were not able to reach dst at all.
+Bellmon ford:- this is simpler than Dijkstra's Algorithm and easier to write.
+Start with the cost array with all the values as max. Set the src idx as 0.
+for k+1 times we run following loop. At each iteration we create a copy of the cost array. and iterate over given array of edges. we check if the current source value is max in the original cost array, if yes that means we havnt reached that src node yet, so continue. if not then we check if the current edge cost + cost of src node from original array is &lt; cost of dst node in copy array if yes update the dst node cost in copy array. 
+After the interation over all the loops is done. set the original array to copy array</t>
+  </si>
+  <si>
+    <t>Replace the Substring for Balanced String - LeetCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Window can be said when all the Characters are &lt;= the expected char count.
+We will first iterate over the given string and find the freq of all the characters.
+Then we will start the sliding window. As we go over the the string string sutract the count from the freqency of the character at right pointer. when the window gets valid as per the above statement we start srinking the window from left and adding the frequency of the character at left pointer. before shrinking check if the window size is minimum. </t>
+  </si>
+  <si>
+    <t>Use array to count frequencies so that you don’t have to deal with nulls and map.compute if absent</t>
   </si>
 </sst>
 </file>
@@ -2025,6 +2973,1316 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC764995-FCA0-4529-9EFB-623E5BA63091}">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="33.21875" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="96.88671875" customWidth="1"/>
+    <col min="4" max="4" width="58.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D4" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D6" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="187.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="https://leetcode.com/problems/number-of-islands/" xr:uid="{42D103E7-A31F-457A-B665-913C0867C89F}"/>
+    <hyperlink ref="A3" r:id="rId2" display="https://leetcode.com/problems/clone-graph/" xr:uid="{BD2E07DF-1CAE-4B5E-848B-20B3C58AF819}"/>
+    <hyperlink ref="A4" r:id="rId3" display="https://leetcode.com/problems/max-area-of-island/" xr:uid="{5B368448-1B14-4364-B8C9-67E86E0D4612}"/>
+    <hyperlink ref="A5" r:id="rId4" display="https://leetcode.com/problems/pacific-atlantic-water-flow/" xr:uid="{4C2FDA89-4B51-4DD4-B6FE-618A74F822A2}"/>
+    <hyperlink ref="A6" r:id="rId5" display="https://leetcode.com/problems/surrounded-regions/description/" xr:uid="{C7320658-E262-4B91-9055-198A08A76550}"/>
+    <hyperlink ref="A7" r:id="rId6" display="https://leetcode.com/problems/rotting-oranges/description/" xr:uid="{17AB8D81-B11B-458C-B0CF-A0D3A25BD344}"/>
+    <hyperlink ref="A8" r:id="rId7" display="https://leetcode.com/problems/walls-and-gates/" xr:uid="{9134C79A-D7B0-400A-94EB-3AA215D6CC34}"/>
+    <hyperlink ref="A9" r:id="rId8" display="https://leetcode.com/problems/course-schedule/description/" xr:uid="{8D7C527B-5F34-4C28-BA76-DA34CAF68760}"/>
+    <hyperlink ref="A10" r:id="rId9" display="https://leetcode.com/problems/course-schedule-ii/description/" xr:uid="{C4861FB0-B27F-4930-AC48-09568FCB7E8A}"/>
+    <hyperlink ref="A11" r:id="rId10" display="https://leetcode.com/problems/redundant-connection/description/" xr:uid="{A89B60F3-0400-40B1-85D1-DB1106C30E01}"/>
+    <hyperlink ref="A12" r:id="rId11" display="https://leetcode.com/problems/number-of-connected-components-in-an-undirected-graph/description/" xr:uid="{425E98E5-E659-4A64-8A10-4B689FC4AAB2}"/>
+    <hyperlink ref="A13" r:id="rId12" display="https://leetcode.com/problems/graph-valid-tree/" xr:uid="{0515F0F4-B850-4EC8-B345-5E45DCF8A8D9}"/>
+    <hyperlink ref="A14" r:id="rId13" display="https://leetcode.com/problems/word-ladder/" xr:uid="{0D0B5DCF-A2CC-4107-9F0B-25D463314A58}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A4EE6B3-2219-4696-A9DF-79D568FB8D12}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26.6640625" customWidth="1"/>
+    <col min="2" max="2" width="17.88671875" customWidth="1"/>
+    <col min="3" max="4" width="62.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="https://leetcode.com/problems/reconstruct-itinerary/description/" xr:uid="{DD744549-32EB-47A7-9FA5-E9E84890B098}"/>
+    <hyperlink ref="A3" r:id="rId2" display="https://leetcode.com/problems/min-cost-to-connect-all-points/description/" xr:uid="{E53B2327-B47B-42F9-A92C-8B47B2ABAA05}"/>
+    <hyperlink ref="A4" r:id="rId3" display="https://leetcode.com/problems/network-delay-time/description/" xr:uid="{6D42273D-8790-4D10-AA2E-E82FC2EE20EB}"/>
+    <hyperlink ref="A5" r:id="rId4" display="https://leetcode.com/problems/swim-in-rising-water/description/" xr:uid="{76200CCA-4AAD-4522-848A-8EB0D462EF4F}"/>
+    <hyperlink ref="A6" r:id="rId5" display="https://leetcode.com/problems/alien-dictionary/description/" xr:uid="{0B35CB0B-4D22-4E0D-8656-AD50CA17EF51}"/>
+    <hyperlink ref="A7" r:id="rId6" display="https://leetcode.com/problems/cheapest-flights-within-k-stops/description/" xr:uid="{8315DF07-5111-4612-8E5E-6D0187187543}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE13C37F-11A3-4397-8B8D-9DCEBD999469}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26.77734375" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" customWidth="1"/>
+    <col min="3" max="3" width="75.5546875" customWidth="1"/>
+    <col min="4" max="4" width="75.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D4" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="https://leetcode.com/problems/climbing-stairs/description/" xr:uid="{4CBE2F25-3423-47F7-84E4-11FA7387E3AB}"/>
+    <hyperlink ref="A3" r:id="rId2" display="https://leetcode.com/problems/min-cost-climbing-stairs/description/" xr:uid="{6ABDA180-44C6-445F-9F4A-DBE3CD4B2A42}"/>
+    <hyperlink ref="A4" r:id="rId3" display="https://leetcode.com/problems/house-robber/description/" xr:uid="{9B07FDD1-DD18-48C4-A1C7-CFD02A0E3D6A}"/>
+    <hyperlink ref="A5" r:id="rId4" display="https://leetcode.com/problems/house-robber-ii/" xr:uid="{4F93DCCB-3D1A-4A41-A998-AB596F802C23}"/>
+    <hyperlink ref="A6" r:id="rId5" display="https://leetcode.com/problems/longest-palindromic-substring/" xr:uid="{CA634C21-4BAE-44A2-AB57-D600CE164CF1}"/>
+    <hyperlink ref="A7" r:id="rId6" display="https://leetcode.com/problems/palindromic-substrings/description/" xr:uid="{196EDA87-3033-4B7F-89D6-D40A4BD7E291}"/>
+    <hyperlink ref="A8" r:id="rId7" display="https://leetcode.com/problems/decode-ways/" xr:uid="{7840808B-5E54-4A2C-95D6-6319121A1809}"/>
+    <hyperlink ref="A9" r:id="rId8" display="https://leetcode.com/problems/coin-change/" xr:uid="{671F4503-9067-4610-8B12-FF3B50E886F0}"/>
+    <hyperlink ref="A10" r:id="rId9" display="https://leetcode.com/problems/maximum-product-subarray/description/" xr:uid="{C1C8F071-7BAE-4F85-88DF-AB2C7F664A87}"/>
+    <hyperlink ref="A11" r:id="rId10" display="https://leetcode.com/problems/word-break/description/" xr:uid="{3C5965F4-CC6C-4A35-BC09-327F54B59F1B}"/>
+    <hyperlink ref="A12" r:id="rId11" display="https://leetcode.com/problems/longest-increasing-subsequence/" xr:uid="{2625BF5F-F4E2-4EE2-ACD1-21CA5738C744}"/>
+    <hyperlink ref="A13" r:id="rId12" display="https://leetcode.com/problems/partition-equal-subset-sum/" xr:uid="{E34ECFB4-2D21-489A-9B78-D8E73A24E785}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07C64653-15EB-4BE4-A0BE-8C803CA41122}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30.6640625" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" customWidth="1"/>
+    <col min="3" max="3" width="71.109375" customWidth="1"/>
+    <col min="4" max="4" width="79.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="360" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="https://leetcode.com/problems/unique-paths/description/" xr:uid="{1968DB57-ADF7-4DA9-8C9D-01D3E9F77780}"/>
+    <hyperlink ref="A3" r:id="rId2" display="https://leetcode.com/problems/longest-common-subsequence/description/" xr:uid="{2283E035-A797-40ED-84D6-F22E951465F6}"/>
+    <hyperlink ref="A4" r:id="rId3" display="https://leetcode.com/problems/best-time-to-buy-and-sell-stock-with-cooldown/description/" xr:uid="{F9E28E46-2417-4881-B019-C64A03F916CC}"/>
+    <hyperlink ref="A5" r:id="rId4" display="https://leetcode.com/problems/coin-change-ii/" xr:uid="{84F1777A-378F-4090-9CFB-DC5DA9D2C30C}"/>
+    <hyperlink ref="A6" r:id="rId5" display="https://leetcode.com/problems/target-sum/description/" xr:uid="{90C68F1B-CE93-4EEB-B850-D611FCFBD10B}"/>
+    <hyperlink ref="A7" r:id="rId6" display="https://leetcode.com/problems/interleaving-string/description/" xr:uid="{EB2612EF-5BDA-4D5C-8B0E-A84387DD0249}"/>
+    <hyperlink ref="A8" r:id="rId7" display="https://leetcode.com/problems/longest-increasing-path-in-a-matrix/description/" xr:uid="{57E8DED0-C959-4B8C-BDFE-0A52151A937B}"/>
+    <hyperlink ref="A9" r:id="rId8" display="https://leetcode.com/problems/distinct-subsequences/" xr:uid="{5D3870E4-7190-4B96-A9B1-17AD649626E2}"/>
+    <hyperlink ref="A10" r:id="rId9" display="https://leetcode.com/problems/edit-distance/description/" xr:uid="{F875C647-64BB-4F5D-A0EE-44A328FE6F1F}"/>
+    <hyperlink ref="A11" r:id="rId10" display="https://leetcode.com/problems/burst-balloons/" xr:uid="{3054EACB-54F7-4DFD-A8E1-DAEAE3707B6A}"/>
+    <hyperlink ref="A12" r:id="rId11" display="https://leetcode.com/problems/regular-expression-matching/description/" xr:uid="{ED3933D0-9ECA-4ABD-B5CE-02AC617BB630}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2445BE4B-358C-45BA-8A7F-7C0BF25D2C52}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="32.21875" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="82.33203125" customWidth="1"/>
+    <col min="4" max="4" width="76.77734375" customWidth="1"/>
+    <col min="5" max="5" width="26.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="https://leetcode.com/problems/maximum-subarray/description/" xr:uid="{665774A8-3287-4CFA-BE32-6AB618FB4F3A}"/>
+    <hyperlink ref="A3" r:id="rId2" display="https://leetcode.com/problems/jump-game/description/" xr:uid="{CE0B42D3-99F9-445E-BD54-58F28C7BD5EC}"/>
+    <hyperlink ref="A4" r:id="rId3" display="https://leetcode.com/problems/jump-game-ii/description/" xr:uid="{9B5E12F2-26FF-458C-852C-6C1E976D55BC}"/>
+    <hyperlink ref="A5" r:id="rId4" display="https://leetcode.com/problems/gas-station/" xr:uid="{48C7CF87-BEA6-4A9F-B7EE-F9526C240E08}"/>
+    <hyperlink ref="A6" r:id="rId5" display="https://leetcode.com/problems/hand-of-straights/" xr:uid="{ACDC9A53-1EEC-4487-8606-F2964628FDFA}"/>
+    <hyperlink ref="A7" r:id="rId6" display="https://leetcode.com/problems/merge-triplets-to-form-target-triplet/" xr:uid="{9C63BBAC-DD89-496A-B8C8-8D412AAB3D5F}"/>
+    <hyperlink ref="A8" r:id="rId7" display="https://leetcode.com/problems/partition-labels/description/" xr:uid="{3D79D6C2-7396-447A-ACB4-5D7D266E70FE}"/>
+    <hyperlink ref="A9" r:id="rId8" display="https://leetcode.com/problems/valid-parenthesis-string/description/" xr:uid="{9F2DFAFC-77A8-476D-9C92-DD147D737B1E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD2F9DAC-B7A2-4EB0-BCDF-CE05DAB5226C}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="31.88671875" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" customWidth="1"/>
+    <col min="3" max="3" width="62" customWidth="1"/>
+    <col min="4" max="4" width="62.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="D3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D4" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D5" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="143.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="https://leetcode.com/problems/meeting-rooms/" xr:uid="{AF6BABF4-5A4E-49E4-B694-DDCD3C7CDD76}"/>
+    <hyperlink ref="A3" r:id="rId2" display="https://leetcode.com/problems/meeting-rooms-ii/description/" xr:uid="{931351B1-F689-49C1-BFB3-63F446C62708}"/>
+    <hyperlink ref="A4" r:id="rId3" display="https://leetcode.com/problems/insert-interval/description/" xr:uid="{1D902C08-5650-490A-8FE7-0CC055D36AAC}"/>
+    <hyperlink ref="A5" r:id="rId4" display="https://leetcode.com/problems/merge-intervals/description/" xr:uid="{CA8FD094-C035-4F98-A678-20455357BC02}"/>
+    <hyperlink ref="A6" r:id="rId5" display="https://leetcode.com/problems/non-overlapping-intervals/description/" xr:uid="{A74233C3-A456-4F43-AB77-B9DC106C1AE8}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{371645DA-3C6D-4912-A3CD-3114D5FFB809}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26.6640625" customWidth="1"/>
+    <col min="2" max="2" width="17.88671875" customWidth="1"/>
+    <col min="3" max="3" width="62.21875" customWidth="1"/>
+    <col min="4" max="4" width="71.109375" customWidth="1"/>
+    <col min="5" max="5" width="35.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" display="https://leetcode.com/problems/rotate-image/description/" xr:uid="{D05508D2-70C0-42D2-BCAE-952B19C70094}"/>
+    <hyperlink ref="A5" r:id="rId2" display="https://leetcode.com/problems/spiral-matrix/" xr:uid="{F850B489-9CF6-4AAE-9B24-FED7426548E2}"/>
+    <hyperlink ref="A6" r:id="rId3" display="https://leetcode.com/problems/set-matrix-zeroes/submissions/1980220660/" xr:uid="{543E6995-A1DD-4DED-9F5D-8296D1A59334}"/>
+    <hyperlink ref="A2" r:id="rId4" display="https://leetcode.com/problems/happy-number/" xr:uid="{B203D9E8-62AF-4981-8666-2CD2E4D3B07A}"/>
+    <hyperlink ref="A3" r:id="rId5" display="https://leetcode.com/problems/plus-one/" xr:uid="{46382E58-9D64-4256-A8B1-47AB2A7693EB}"/>
+    <hyperlink ref="A7" r:id="rId6" display="https://leetcode.com/problems/powx-n/description/" xr:uid="{143B9DF2-B146-4562-8989-D3FAD506714B}"/>
+    <hyperlink ref="A8" r:id="rId7" display="https://leetcode.com/problems/multiply-strings/description/" xr:uid="{657E44DB-AC0C-4DCC-AF2B-887DDE3BC693}"/>
+    <hyperlink ref="A9" r:id="rId8" display="https://leetcode.com/problems/detect-squares/description/" xr:uid="{054C6133-0936-454C-8F8B-B9FF1A24AA04}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51EFE547-12EF-471A-9F31-64A493928DEC}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.44140625" customWidth="1"/>
+    <col min="2" max="2" width="24.88671875" customWidth="1"/>
+    <col min="3" max="3" width="64.109375" customWidth="1"/>
+    <col min="4" max="4" width="57.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D7" t="s">
+        <v>436</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="https://leetcode.com/problems/single-number/description/" xr:uid="{2367A233-73DB-471D-B7DB-46C69D091664}"/>
+    <hyperlink ref="A3" r:id="rId2" display="https://leetcode.com/problems/number-of-1-bits/" xr:uid="{712B4552-90BC-427B-A966-F30D42BCD3B5}"/>
+    <hyperlink ref="A4" r:id="rId3" display="https://leetcode.com/problems/counting-bits/description/" xr:uid="{7EEA22EB-C8F9-4DF5-B6DA-3B1B6766B07C}"/>
+    <hyperlink ref="A5" r:id="rId4" display="https://leetcode.com/problems/reverse-bits/submissions/1987174869/" xr:uid="{063EAA42-1DF1-42AF-9FB5-F7EB3ACD48EA}"/>
+    <hyperlink ref="A6" r:id="rId5" display="https://leetcode.com/problems/missing-number/description/" xr:uid="{9B4C4E79-D7A3-41A9-9C63-CE8A31E6DF30}"/>
+    <hyperlink ref="A7" r:id="rId6" display="https://leetcode.com/problems/reverse-integer/" xr:uid="{11CCDFC9-DF62-4DD6-B25E-58EC54D96DC3}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C831D45-5F73-4BB4-A940-A583DFCF0C9C}">
   <dimension ref="A1:E6"/>
@@ -2158,7 +4416,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F2A168C-7804-47B0-992A-464C7DE20227}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="50" bestFit="1" customWidth="1"/>
@@ -2253,37 +4511,52 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="B6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="B7" t="s">
         <v>34</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2297,10 +4570,11 @@
     <hyperlink ref="E4" r:id="rId6" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/LongestRepeatingCharacterReplacement.java" xr:uid="{E815522C-A80C-4406-8726-FBDA4F80439C}"/>
     <hyperlink ref="A5" r:id="rId7" display="https://leetcode.com/problems/permutation-in-string/description/" xr:uid="{6693C9A1-565E-455A-9D84-7DDDC14D5CEA}"/>
     <hyperlink ref="E5" r:id="rId8" display="https://github.com/reaper131299/leetcode/blob/main/src/medium/PermutationInString.java" xr:uid="{6A803160-169B-4AFD-B7D8-8A656C473D34}"/>
-    <hyperlink ref="A6" r:id="rId9" display="https://leetcode.com/problems/minimum-window-substring/description/" xr:uid="{CABCB7D2-EDD7-44C1-986F-369D680899CE}"/>
-    <hyperlink ref="E6" r:id="rId10" display="https://github.com/reaper131299/leetcode/blob/main/src/hard/MinimumWindowSubstring.java" xr:uid="{D7BC186D-98D2-4985-A3C1-35FC4B59A8F5}"/>
-    <hyperlink ref="A7" r:id="rId11" display="https://leetcode.com/problems/sliding-window-maximum/description/" xr:uid="{41649E92-7496-40A8-91FE-BC2AD33112D4}"/>
-    <hyperlink ref="E7" r:id="rId12" display="https://github.com/reaper131299/leetcode/blob/main/src/hard/SlidingWindowMaximum.java" xr:uid="{A60EF5BD-47AB-49CB-A051-E6DA4FFDFC06}"/>
+    <hyperlink ref="A7" r:id="rId9" display="https://leetcode.com/problems/minimum-window-substring/description/" xr:uid="{CABCB7D2-EDD7-44C1-986F-369D680899CE}"/>
+    <hyperlink ref="E7" r:id="rId10" display="https://github.com/reaper131299/leetcode/blob/main/src/hard/MinimumWindowSubstring.java" xr:uid="{D7BC186D-98D2-4985-A3C1-35FC4B59A8F5}"/>
+    <hyperlink ref="A8" r:id="rId11" display="https://leetcode.com/problems/sliding-window-maximum/description/" xr:uid="{41649E92-7496-40A8-91FE-BC2AD33112D4}"/>
+    <hyperlink ref="E8" r:id="rId12" display="https://github.com/reaper131299/leetcode/blob/main/src/hard/SlidingWindowMaximum.java" xr:uid="{A60EF5BD-47AB-49CB-A051-E6DA4FFDFC06}"/>
+    <hyperlink ref="A6" r:id="rId13" display="https://leetcode.com/problems/replace-the-substring-for-balanced-string/description/" xr:uid="{611A0924-261A-4374-A891-059B588BA4E8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
